--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$180</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1752,69 +1752,69 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Starship Scarlet Bronze Leaf'</t>
+          <t>Abelia 'Radiance'</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Lobelia × speciosa 'Starship Scarlet Bronze Leaf'</t>
+          <t>Abelia × grandiflora 'Radiance'</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade. Best flowering with at least half a day of sun.</t>
+          <t>Full sun to partial shade; foliage colour is strongest with good light.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist; do not allow the compost to dry out in summer.</t>
+          <t>Water deeply while establishing, then only in prolonged dry spells. Keep the root zone freely drained.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while it establishes. Deadhead spent spikes; mulch the crown for winter and avoid stagnant soil.</t>
+          <t>Mulch while it settles, keeping mulch clear of the stems. Prune lightly after flowering to maintain a compact framework; remove winter-damaged tips in spring.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Bronze foliage from spring; tall scarlet flower spikes July–September; dies back in winter and returns from the crown.</t>
+          <t>Variegated green, cream and yellow foliage carries warm pink-red tones in cooler weather; small white summer flowers; semi-evergreen in mild winters.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Bed 5</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Wisteria</t>
+          <t>Lobelia 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Wisteria spp.</t>
+          <t>Lobelia × speciosa 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade. Best flowering with at least half a day of sun.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Deep watering when young; established plants tolerate drought.</t>
+          <t>Keep evenly moist; do not allow the compost to dry out in summer.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Prune twice yearly: August (long shoots to 6 leaves) and February (back to 2–3 buds).</t>
+          <t>Keep evenly moist while it establishes. Deadhead spent spikes; mulch the crown for winter and avoid stagnant soil.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Lilac racemes May; bare gnarled stems winter.</t>
+          <t>Bronze foliage from spring; tall scarlet flower spikes July–September; dies back in winter and returns from the crown.</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Wisteria</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Wisteria spp.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Deep watering when young; established plants tolerate drought.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Prune in late winter. Feed in spring and after first flush.</t>
+          <t>Prune twice yearly: August (long shoots to 6 leaves) and February (back to 2–3 buds).</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–September; bare winter.</t>
+          <t>Lilac racemes May; bare gnarled stems winter.</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax (cultivar to confirm)</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Phormium (cultivar to confirm)</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; shelter from cold drying winds.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid prolonged waterlogging.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Grow in fertile, well-drained soil. Remove damaged leaves at the base in spring and mulch the crown before hard frost. Cultivar still needs confirmation from a label or diagnostic photos.</t>
+          <t>Prune in late winter. Feed in spring and after first flush.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Evergreen sword-shaped foliage year-round; mature plants may produce tall flower stems in summer.</t>
+          <t>Flowers June–September; bare winter.</t>
         </is>
       </c>
     </row>
@@ -1900,32 +1900,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Alstroemeria</t>
+          <t>New Zealand Flax (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Alstroemeria hybrid</t>
+          <t>Phormium (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowering is strongest with plenty of light.</t>
+          <t>Full sun to partial shade; shelter from cold drying winds.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in the growing season, but never waterlogged.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid prolonged waterlogging.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly while flowering. Pull spent flower stems cleanly from the base rather than cutting them. Protect the pot from hard frost in winter.</t>
+          <t>Grow in fertile, well-drained soil. Remove damaged leaves at the base in spring and mulch the crown before hard frost. Cultivar still needs confirmation from a label or diagnostic photos.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Red-and-gold flowers from summer into autumn above dark foliage; dies back in cold weather.</t>
+          <t>Evergreen sword-shaped foliage year-round; mature plants may produce tall flower stems in summer.</t>
         </is>
       </c>
     </row>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Bee's Knees'</t>
+          <t>Alstroemeria</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Bee's Knees'</t>
+          <t>Alstroemeria hybrid</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the most flowers; tolerates light partial shade.</t>
+          <t>Full sun to partial shade; flowering is strongest with plenty of light.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Water when the top of the compost begins to dry; pots may need daily checks in hot weather.</t>
+          <t>Keep evenly moist in the growing season, but never waterlogged.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with a high-potash liquid feed and deadhead or trim leggy growth to keep flowers coming.</t>
+          <t>Feed weekly while flowering. Pull spent flower stems cleanly from the base rather than cutting them. Protect the pot from hard frost in winter.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Clear yellow flowers from summer until the first frost; grown as a tender annual.</t>
+          <t>Red-and-gold flowers from summer into autumn above dark foliage; dies back in cold weather.</t>
         </is>
       </c>
     </row>
@@ -1974,32 +1974,32 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Petunia 'Bee's Knees'</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Petunia 'Bee's Knees'</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; the yellow-and-green foliage colours best in bright indirect light or partial shade.</t>
+          <t>Full sun for the most flowers; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly between waterings, without letting the pot dry out completely.</t>
+          <t>Water when the top of the compost begins to dry; pots may need daily checks in hot weather.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape. Hardy and evergreen, but vigorous if later planted into open ground.</t>
+          <t>Feed weekly with a high-potash liquid feed and deadhead or trim leggy growth to keep flowers coming.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Golden variegated foliage year-round with small violet-blue flowers mainly in spring.</t>
+          <t>Clear yellow flowers from summer until the first frost; grown as a tender annual.</t>
         </is>
       </c>
     </row>
@@ -2011,32 +2011,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Nemesia</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nemesia hybrid</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; a little afternoon shade helps during hot spells.</t>
+          <t>Sun to shade; the yellow-and-green foliage colours best in bright indirect light or partial shade.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but not waterlogged; check the pot frequently in warm or windy weather.</t>
+          <t>Moderate. Let the surface dry slightly between waterings, without letting the pot dry out completely.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Feed fortnightly while flowering. Deadhead or trim back tired stems by about a third to encourage a fresh flush.</t>
+          <t>Trim trailing stems to shape. Hardy and evergreen, but vigorous if later planted into open ground.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Small, scented flowers from summer into autumn; usually grown as tender seasonal colour.</t>
+          <t>Golden variegated foliage year-round with small violet-blue flowers mainly in spring.</t>
         </is>
       </c>
     </row>
@@ -2048,32 +2048,32 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Lythrum 'Robin'</t>
+          <t>Nemesia</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lythrum salicaria 'Robin'</t>
+          <t>Nemesia hybrid</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers best in full sun.</t>
+          <t>Full sun to light partial shade; a little afternoon shade helps during hot spells.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Keep the compost consistently moist, especially during flowering.</t>
+          <t>Keep the compost evenly moist but not waterlogged; check the pot frequently in warm or windy weather.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering or leave some seedheads for wildlife. Cut old stems down in late winter or early spring.</t>
+          <t>Feed fortnightly while flowering. Deadhead or trim back tired stems by about a third to encourage a fresh flush.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dense magenta flower spikes in summer, popular with bees; herbaceous and dormant in winter.</t>
+          <t>Small, scented flowers from summer into autumn; usually grown as tender seasonal colour.</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Begonia 'Carmen'</t>
+          <t>Lythrum 'Robin'</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Begonia 'Carmen'</t>
+          <t>Lythrum salicaria 'Robin'</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Bright partial shade or gentle morning sun; protect from harsh midday sun.</t>
+          <t>Full sun to partial shade; flowers best in full sun.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but not saturated. Water the compost rather than the leaves and flowers.</t>
+          <t>Moisture-loving. Keep the compost consistently moist, especially during flowering.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded blooms and feed fortnightly in summer. Tender — protect from frost and overwinter under cover if keeping it.</t>
+          <t>Deadhead to prolong flowering or leave some seedheads for wildlife. Cut old stems down in late winter or early spring.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Double red flowers through summer and early autumn; tender and dormant or discarded after frost.</t>
+          <t>Dense magenta flower spikes in summer, popular with bees; herbaceous and dormant in winter.</t>
         </is>
       </c>
     </row>
@@ -2122,32 +2122,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Aroma Heart of Gold'</t>
+          <t>Begonia 'Carmen'</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nemesia Aroma Heart of Gold (Aroma Series)</t>
+          <t>Begonia 'Carmen'</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Bright partial shade or gentle morning sun; protect from harsh midday sun.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, watering in dry spells to maintain flowering.</t>
+          <t>Keep evenly moist but not saturated. Water the compost rather than the leaves and flowers.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Pinch the growing tips for a bushy plant. Trim flowering shoots after the first flush to encourage more blooms; protect cuttings from frost if overwintering.</t>
+          <t>Deadhead faded blooms and feed fortnightly in summer. Tender — protect from frost and overwinter under cover if keeping it.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Sweetly fragrant burgundy-red and creamy-yellow flowers with burnt-orange centres from summer into autumn.</t>
+          <t>Double red flowers through summer and early autumn; tender and dormant or discarded after frost.</t>
         </is>
       </c>
     </row>
@@ -2159,49 +2159,49 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cabbage Tree</t>
+          <t>Nemesia 'Aroma Heart of Gold'</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Cordyline australis 'Red Star'</t>
+          <t>Nemesia Aroma Heart of Gold (Aroma Series)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Moderate; established plants tolerate drought.</t>
+          <t>Keep moist but well drained, watering in dry spells to maintain flowering.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tie up leaves in winter to protect crown if hard frost forecast.</t>
+          <t>Pinch the growing tips for a bushy plant. Trim flowering shoots after the first flush to encourage more blooms; protect cuttings from frost if overwintering.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Evergreen burgundy fountain of leaves.</t>
+          <t>Sweetly fragrant burgundy-red and creamy-yellow flowers with burnt-orange centres from summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 5</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Houseleeks</t>
+          <t>Cabbage Tree</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum</t>
+          <t>Cordyline australis 'Red Star'</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2211,17 +2211,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Very low. Hates wet.</t>
+          <t>Moderate; established plants tolerate drought.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Sharp drainage; almost no maintenance.</t>
+          <t>Tie up leaves in winter to protect crown if hard frost forecast.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes; flowering rosettes die after blooming, replaced by offsets.</t>
+          <t>Evergreen burgundy fountain of leaves.</t>
         </is>
       </c>
     </row>
@@ -2233,32 +2233,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Echeveria</t>
+          <t>Houseleeks</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Echeveria cultivar</t>
+          <t>Sempervivum</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Full sun or very bright light; acclimatise gradually to strong sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Low. Water only when the soil has dried; keep almost dry in winter.</t>
+          <t>Very low. Hates wet.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Sharply drained soil. Tender: lift before frost and overwinter frost-free under cover.</t>
+          <t>Sharp drainage; almost no maintenance.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Evergreen powdery grey-purple rosette; pink-red flower stems may appear in summer.</t>
+          <t>Evergreen rosettes; flowering rosettes die after blooming, replaced by offsets.</t>
         </is>
       </c>
     </row>
@@ -2270,32 +2270,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Chocolate Ball'</t>
+          <t>Echeveria</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Sedum polytrichoides 'Chocolate Ball'</t>
+          <t>Echeveria cultivar</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun or very bright light; acclimatise gradually to strong sun.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Very low; let the gritty soil dry between waterings.</t>
+          <t>Low. Water only when the soil has dried; keep almost dry in winter.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Sharp drainage is essential. RHS H3: protect from severe frost and prolonged winter wet.</t>
+          <t>Sharply drained soil. Tender: lift before frost and overwinter frost-free under cover.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Evergreen bronze-brown foliage; small yellow flowers in summer.</t>
+          <t>Evergreen powdery grey-purple rosette; pink-red flower stems may appear in summer.</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Older Caucasian Stonecrop</t>
+          <t>Sedum 'Chocolate Ball'</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Phedimus spurius cultivar</t>
+          <t>Sedum polytrichoides 'Chocolate Ball'</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and strongest colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Low; water only during establishment or prolonged drought.</t>
+          <t>Very low; let the gritty soil dry between waterings.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Trim spent flower stems and pull wandering shoots back from smaller alpines. Keep the crown sharply drained.</t>
+          <t>Sharp drainage is essential. RHS H3: protect from severe frost and prolonged winter wet.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Scalloped green leaves flush red; pink-red flower clusters age to brown seedheads.</t>
+          <t>Evergreen bronze-brown foliage; small yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2344,32 +2344,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Common Houseleek</t>
+          <t>Older Caucasian Stonecrop</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum tectorum</t>
+          <t>Phedimus spurius cultivar</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun for compact growth and strongest colour.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Very low; established rosettes normally need no extra water.</t>
+          <t>Low; water only during establishment or prolonged drought.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Keep grit around the crowns, clear trapped leaves and remove a parent rosette only after it flowers and dies naturally.</t>
+          <t>Trim spent flower stems and pull wandering shoots back from smaller alpines. Keep the crown sharply drained.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes colour more strongly in cold or bright conditions; starry flowers may appear in summer.</t>
+          <t>Scalloped green leaves flush red; pink-red flower clusters age to brown seedheads.</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Six-rowed Stonecrop</t>
+          <t>Common Houseleek</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Sedum sexangulare</t>
+          <t>Sempervivum tectorum</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Very low once rooted.</t>
+          <t>Very low; established rosettes normally need no extra water.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Use gritty, lean soil and trim spreading stems where they crowd slower alpines.</t>
+          <t>Keep grit around the crowns, clear trapped leaves and remove a parent rosette only after it flowers and dies naturally.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Evergreen cylindrical leaves in six neat ranks; yellow star flowers in summer.</t>
+          <t>Evergreen rosettes colour more strongly in cold or bright conditions; starry flowers may appear in summer.</t>
         </is>
       </c>
     </row>
@@ -2418,32 +2418,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Fancy Finch'</t>
+          <t>Six-rowed Stonecrop</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Fanfin' (Feathered Friends Fancy Finch)</t>
+          <t>Sedum sexangulare</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Partial shade; protect the golden foliage from scorching midday sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist while establishing.</t>
+          <t>Very low once rooted.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Trim spent flower spikes and remove runners that stray into the driest succulent pockets.</t>
+          <t>Use gritty, lean soil and trim spreading stems where they crowd slower alpines.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Golden to orange narrow foliage year-round; blue flower spikes in spring.</t>
+          <t>Evergreen cylindrical leaves in six neat ranks; yellow star flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2455,32 +2455,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Snowflake'</t>
+          <t>Ajuga 'Fancy Finch'</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea quercifolia 'Brido' (Snowflake)</t>
+          <t>Ajuga 'Fanfin' (Feathered Friends Fancy Finch)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shade is useful in hot weather.</t>
+          <t>Partial shade; protect the golden foliage from scorching midday sun.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Moderate to high while establishing; soak deeply during dry spells.</t>
+          <t>Moderate. Keep evenly moist while establishing.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Give it a humus-rich pocket beneath the gravel, mulch clear of the crown and prune only dead or misplaced wood after flowering.</t>
+          <t>Trim spent flower spikes and remove runners that stray into the driest succulent pockets.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Double white flower panicles fade pink; oak-shaped leaves turn rich red and purple in autumn.</t>
+          <t>Golden to orange narrow foliage year-round; blue flower spikes in spring.</t>
         </is>
       </c>
     </row>
@@ -2492,32 +2492,32 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chick Charms Houseleek Mix</t>
+          <t>Hydrangea 'Snowflake'</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum Chick Charms Series</t>
+          <t>Hydrangea quercifolia 'Brido' (Snowflake)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade; afternoon shade is useful in hot weather.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Very low; only newly planted offsets need occasional water.</t>
+          <t>Moderate to high while establishing; soak deeply during dry spells.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>The label confirms the series but not its individual cultivars. Keep crowns dry and remove spent flowering rosettes.</t>
+          <t>Give it a humus-rich pocket beneath the gravel, mulch clear of the crown and prune only dead or misplaced wood after flowering.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes change colour with season and temperature; mature rosettes may flower in summer.</t>
+          <t>Double white flower panicles fade pink; oak-shaped leaves turn rich red and purple in autumn.</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Achillea 'King Alfred'</t>
+          <t>Chick Charms Houseleek Mix</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Achillea 'King Alfred'</t>
+          <t>Sempervivum Chick Charms Series</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Very low; only newly planted offsets need occasional water.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Keep in lean, sharply drained soil and trim untidy growth in spring.</t>
+          <t>The label confirms the series but not its individual cultivars. Keep crowns dry and remove spent flowering rosettes.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Low grey-green aromatic mat with pale yellow flower heads in late spring and early summer.</t>
+          <t>Evergreen rosettes change colour with season and temperature; mature rosettes may flower in summer.</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Golden Stonecrop 'Aureum'</t>
+          <t>Achillea 'King Alfred'</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sedum acre 'Aureum'</t>
+          <t>Achillea 'King Alfred'</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Very low.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Avoid rich soil and trim after flowering if it spreads over slower plants.</t>
+          <t>Keep in lean, sharply drained soil and trim untidy growth in spring.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Evergreen yellow-gold foliage with small yellow flowers in summer.</t>
+          <t>Low grey-green aromatic mat with pale yellow flower heads in late spring and early summer.</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Cobweb Houseleek</t>
+          <t>Golden Stonecrop 'Aureum'</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum arachnoideum</t>
+          <t>Sedum acre 'Aureum'</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Keep winter rain and leaf litter out of the rosettes; detach offsets to extend the colony.</t>
+          <t>Avoid rich soil and trim after flowering if it spreads over slower plants.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Evergreen cobwebbed rosettes, often red-flushed; pink star flowers in summer.</t>
+          <t>Evergreen yellow-gold foliage with small yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Thrift 'Armada White'</t>
+          <t>Cobweb Houseleek</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Armeria maritima 'Armada White'</t>
+          <t>Sempervivum arachnoideum</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate while establishing; drought tolerant later.</t>
+          <t>Very low.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Deadhead the white globes and keep the crown clear in gritty soil.</t>
+          <t>Keep winter rain and leaf litter out of the rosettes; detach offsets to extend the colony.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Evergreen grassy cushions with white flower heads from spring into summer.</t>
+          <t>Evergreen cobwebbed rosettes, often red-flushed; pink star flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Houseleek 'Purple Quartz'</t>
+          <t>Thrift 'Armada White'</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum 'Purple Quartz' (Big Sam Series)</t>
+          <t>Armeria maritima 'Armada White'</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2692,17 +2692,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Very low.</t>
+          <t>Low to moderate while establishing; drought tolerant later.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Provide sharp drainage, clear debris and protect from persistent winter wet rather than cold.</t>
+          <t>Deadhead the white globes and keep the crown clear in gritty soil.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Grey-green rosettes flush pink and purple; mature rosettes flower once before offsets replace them.</t>
+          <t>Evergreen grassy cushions with white flower heads from spring into summer.</t>
         </is>
       </c>
     </row>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Angelina'</t>
+          <t>Houseleek 'Purple Quartz'</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Sedum rupestre 'Angelina'</t>
+          <t>Sempervivum 'Purple Quartz' (Big Sam Series)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest gold and orange colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Very low once established.</t>
+          <t>Very low.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Shear or pull back spreading shoots when they overrun small rosettes.</t>
+          <t>Provide sharp drainage, clear debris and protect from persistent winter wet rather than cold.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Golden needle-like foliage turns orange in cold weather; yellow flowers in summer.</t>
+          <t>Grey-green rosettes flush pink and purple; mature rosettes flower once before offsets replace them.</t>
         </is>
       </c>
     </row>
@@ -2751,32 +2751,32 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Stonecrop 'Dragon's Blood'</t>
+          <t>Sedum 'Angelina'</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Phedimus spurius 'Schorbuser Blut'</t>
+          <t>Sedum rupestre 'Angelina'</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun for strongest gold and orange colour.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Very low once established.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Trim spent heads and keep spreading stems within their allotted gravel pocket.</t>
+          <t>Shear or pull back spreading shoots when they overrun small rosettes.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Green-red scalloped leaves deepen burgundy; clusters of deep pink-red summer flowers.</t>
+          <t>Golden needle-like foliage turns orange in cold weather; yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2788,32 +2788,32 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Echeveria 'Devotion'</t>
+          <t>Stonecrop 'Dragon's Blood'</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Echeveria pulvinata 'Bcec12001' (Devotion)</t>
+          <t>Phedimus spurius 'Schorbuser Blut'</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Full sun or very bright light.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Low; soak only after the root zone dries.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Tender H2: lift before frost and overwinter bright, frost-free and almost dry.</t>
+          <t>Trim spent heads and keep spreading stems within their allotted gravel pocket.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Velvety green leaves develop burgundy margins and tips in strong light and cool weather.</t>
+          <t>Green-red scalloped leaves deepen burgundy; clusters of deep pink-red summer flowers.</t>
         </is>
       </c>
     </row>
@@ -2825,32 +2825,32 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Atlantis'</t>
+          <t>Echeveria 'Devotion'</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Sedum takesimense 'Nonsitnal' (Atlantis)</t>
+          <t>Echeveria pulvinata 'Bcec12001' (Devotion)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun or very bright light.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Low; soak only after the root zone dries.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Cut back old flower stems in spring and divide if the mound opens in the centre.</t>
+          <t>Tender H2: lift before frost and overwinter bright, frost-free and almost dry.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Green leaves with broad cream-yellow margins blush pink in autumn; yellow summer flowers.</t>
+          <t>Velvety green leaves develop burgundy margins and tips in strong light and cool weather.</t>
         </is>
       </c>
     </row>
@@ -2862,32 +2862,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Purple Fountain Grass 'Rubrum'</t>
+          <t>Sedum 'Atlantis'</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Pennisetum advena 'Rubrum'</t>
+          <t>Sedum takesimense 'Nonsitnal' (Atlantis)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Moderate during active growth; never leave waterlogged.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Tender H3: lift or pot before hard frost and overwinter frost-free; fleece alone is unreliable in Bromsgrove.</t>
+          <t>Cut back old flower stems in spring and divide if the mound opens in the centre.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Arching burgundy leaves and purple-brown bottlebrush plumes from summer into autumn.</t>
+          <t>Green leaves with broad cream-yellow margins blush pink in autumn; yellow summer flowers.</t>
         </is>
       </c>
     </row>
@@ -2899,32 +2899,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Midnight Mystery'</t>
+          <t>Purple Fountain Grass 'Rubrum'</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Ajuga reptans 'Midnight Mystery'</t>
+          <t>Pennisetum advena 'Rubrum'</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Partial shade or gentle sun.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Moderate; keep moist while establishing.</t>
+          <t>Moderate during active growth; never leave waterlogged.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Remove unwanted runners and maintain airflow to reduce mildew.</t>
+          <t>Tender H3: lift or pot before hard frost and overwinter frost-free; fleece alone is unreliable in Bromsgrove.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Dark bronze evergreen foliage with contrasting rosy-pink spring flowers.</t>
+          <t>Arching burgundy leaves and purple-brown bottlebrush plumes from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -2936,32 +2936,32 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax (dark)</t>
+          <t>Ajuga 'Midnight Mystery'</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Phormium 'Platt's Black'</t>
+          <t>Ajuga reptans 'Midnight Mystery'</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade or gentle sun.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Moderate; drought-tolerant once established.</t>
+          <t>Moderate; keep moist while establishing.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Remove old leaves at base. Architectural and low-care.</t>
+          <t>Remove unwanted runners and maintain airflow to reduce mildew.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Evergreen dark foliage year-round.</t>
+          <t>Dark bronze evergreen foliage with contrasting rosy-pink spring flowers.</t>
         </is>
       </c>
     </row>
@@ -2973,69 +2973,69 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Agapanthus</t>
+          <t>New Zealand Flax (dark)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Agapanthus (species and cultivar unknown)</t>
+          <t>Phormium 'Platt's Black'</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable flowering.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Low once established; water during establishment and prolonged late-summer drought.</t>
+          <t>Moderate; drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Grow in moisture-retentive but well-drained soil. Deadhead or retain seedheads deliberately and protect the crown in severe winter weather until hardiness is known.</t>
+          <t>Remove old leaves at base. Architectural and low-care.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Strap-shaped foliage photographed in August; flower colour and exact form remain unresolved.</t>
+          <t>Evergreen dark foliage year-round.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Patio</t>
+          <t>Stone Bed</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Honeysuckle</t>
+          <t>Agapanthus</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Lonicera</t>
+          <t>Agapanthus (species and cultivar unknown)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sun, with shaded roots.</t>
+          <t>Full sun for reliable flowering.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Low once established; water during establishment and prolonged late-summer drought.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering. Train onto support.</t>
+          <t>Grow in moisture-retentive but well-drained soil. Deadhead or retain seedheads deliberately and protect the crown in severe winter weather until hardiness is known.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Fragrant flowers June–August.</t>
+          <t>Strap-shaped foliage photographed in August; flower colour and exact form remain unresolved.</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Clematis</t>
+          <t>Honeysuckle</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Clematis montana</t>
+          <t>Lonicera</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3067,86 +3067,86 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Group 1 clematis — light prune after flowering only. Tie in new growth.</t>
+          <t>Light prune after flowering. Train onto support.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Sheets of pale pink flowers May; vigorous summer growth.</t>
+          <t>Fragrant flowers June–August.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Pear Tree</t>
+          <t>Clematis</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Pyrus</t>
+          <t>Clematis montana</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun, with shaded roots.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Deep watering in dry summers.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape. Thin fruit if heavy.</t>
+          <t>Group 1 clematis — light prune after flowering only. Tie in new growth.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>White blossom April; fruit September; bare winter.</t>
+          <t>Sheets of pale pink flowers May; vigorous summer growth.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Big Pot 1</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia</t>
+          <t>Pear Tree</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia 'Mrs Popple'</t>
+          <t>Pyrus</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Keep compost moist. Water daily in hot weather.</t>
+          <t>Deep watering in dry summers.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+          <t>Winter prune for shape. Thin fruit if heavy.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Red and purple pendant flowers June–October; deciduous in winter; new growth from the base in spring.</t>
+          <t>White blossom April; fruit September; bare winter.</t>
         </is>
       </c>
     </row>
@@ -3158,32 +3158,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Fuchsia</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Showboat Light Pink'</t>
+          <t>Fuchsia 'Mrs Popple'</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out.</t>
+          <t>Keep compost moist. Water daily in hot weather.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowering. Tender annual — replace yearly.</t>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Clusters of soft pink flowers June–October.</t>
+          <t>Red and purple pendant flowers June–October; deciduous in winter; new growth from the base in spring.</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa 'Cabaret Special Pink Star'</t>
+          <t>Verbena 'Showboat Light Pink'</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist. Hates drying out.</t>
+          <t>Regular; don't let compost dry out.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Tender annual.</t>
+          <t>Deadhead to keep flowering. Tender annual — replace yearly.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Pink star-patterned flowers May–October. Continuous if fed.</t>
+          <t>Clusters of soft pink flowers June–October.</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Nepeta</t>
+          <t>Calibrachoa</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nepeta (catmint)</t>
+          <t>Calibrachoa 'Cabaret Special Pink Star'</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Keep evenly moist. Hates drying out.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a repeat. Aromatic — cats love it.</t>
+          <t>Feed weekly with liquid tomato food. Tender annual.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+          <t>Pink star-patterned flowers May–October. Continuous if fed.</t>
         </is>
       </c>
     </row>
@@ -3269,32 +3269,32 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Lobelia</t>
+          <t>Nepeta</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+          <t>Nepeta (catmint)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Keep moist at all times. Hates drying out.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Trim back leggy growth mid-season. Tender annual.</t>
+          <t>Cut back after first flush for a repeat. Aromatic — cats love it.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Deep blue and white trailing flowers May–October.</t>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
         </is>
       </c>
     </row>
@@ -3306,69 +3306,69 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Lobelia</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Midnight Sky'</t>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Keep moist at all times. Hates drying out.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Dark purple-white trumpet flowers May–October.</t>
+          <t>Deep blue and white trailing flowers May–October.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Big Pot 2</t>
+          <t>Big Pot 1</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Lobelia</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+          <t>Petunia 'Midnight Sky'</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Keep moist at all times. Hates drying out.</t>
+          <t>Regular; don't let compost dry out completely.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Trim back leggy growth mid-season. Tender annual.</t>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Deep blue and white trailing flowers May–October.</t>
+          <t>Dark purple-white trumpet flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3380,32 +3380,32 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Lobelia</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Venturi Pink Bicolour'</t>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out.</t>
+          <t>Keep moist at all times. Hates drying out.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowering. Tender annual.</t>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Pink bicolour flower clusters June–October.</t>
+          <t>Deep blue and white trailing flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Sky Purple White Sky'</t>
+          <t>Verbena 'Venturi Pink Bicolour'</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Regular; don't let compost dry out.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Deadhead to keep flowering. Tender annual.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Purple-white striped trumpet flowers May–October.</t>
+          <t>Pink bicolour flower clusters June–October.</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Nepeta</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nepeta (catmint)</t>
+          <t>Petunia 'Sky Purple White Sky'</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3469,17 +3469,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Regular; don't let compost dry out completely.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a repeat. Aromatic.</t>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+          <t>Purple-white striped trumpet flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3491,180 +3491,180 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia</t>
+          <t>Nepeta</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia 'Mrs Popple'</t>
+          <t>Nepeta (catmint)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Keep compost moist. Water daily in hot weather.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+          <t>Cut back after first flush for a repeat. Aromatic.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Red and purple pendant flowers June–October; deciduous in winter.</t>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 1</t>
+          <t>Big Pot 2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Helleborus Ice N' Roses Bennotta</t>
+          <t>Fuchsia</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Helleborus × glandorfensis 'COSEH 6600'</t>
+          <t>Fuchsia 'Mrs Popple'</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to sun in a sheltered position.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist but freely drained; do not leave the crown waterlogged.</t>
+          <t>Keep compost moist. Water daily in hot weather.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Remove tired leaves and faded flower stems in spring. Wear gloves when handling, and raise the pot so winter rain drains freely.</t>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Deep pink to red outward-facing flowers from winter into spring above evergreen foliage.</t>
+          <t>Red and purple pendant flowers June–October; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 2</t>
+          <t>Little Pot 1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis Gold</t>
+          <t>Helleborus Ice N' Roses Bennotta</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis 'Gold'</t>
+          <t>Helleborus × glandorfensis 'COSEH 6600'</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
+          <t>Keep compost evenly moist but freely drained; do not leave the crown waterlogged.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
+          <t>Remove tired leaves and faded flower stems in spring. Wear gloves when handling, and raise the pot so winter rain drains freely.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
+          <t>Deep pink to red outward-facing flowers from winter into spring above evergreen foliage.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Cercis Pot</t>
+          <t>Little Pot 2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cercis 'Carolina Sweetheart'</t>
+          <t>Coreopsis Gold</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Cercis canadensis 'Nccc1'</t>
+          <t>Coreopsis 'Gold'</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
+          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
+          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
+          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Front Pot</t>
+          <t>Cercis Pot</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Sunny Side Up'</t>
+          <t>Cercis 'Carolina Sweetheart'</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Sunny Side Up'</t>
+          <t>Cercis canadensis 'Nccc1'</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade and on overcast days.</t>
+          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
+          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
+          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
+          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Orange Flame'</t>
+          <t>Gazania 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Orange Flame'</t>
+          <t>Gazania rigens 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade.</t>
+          <t>Full sun. Flowers close in shade and on overcast days.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant.</t>
+          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
+          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
+          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa</t>
+          <t>Gazania 'Orange Flame'</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa spp.</t>
+          <t>Gazania rigens 'Orange Flame'</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun. Flowers close in shade.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist. Hates drying out.</t>
+          <t>Low to moderate. Drought-tolerant.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
+          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
+          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3750,143 +3750,143 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Bacopa White</t>
+          <t>Calibrachoa</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata (white cultivar)</t>
+          <t>Calibrachoa spp.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Keep evenly moist. Hates drying out.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 1</t>
+          <t>Front Pot</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Phormium 'Flamingo'</t>
+          <t>Bacopa White</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Phormium 'Flamingo'</t>
+          <t>Sutera cordata (white cultivar)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest foliage colour; shelter from severe cold wind.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then let the upper compost dry slightly; never leave the pot waterlogged.</t>
+          <t>Keep evenly moist.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Remove only damaged leaves at the base. Raise the pot for winter drainage and protect the crown during severe frost.</t>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Evergreen, pink-striped sword-like leaves give year-round structure.</t>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 2</t>
+          <t>Wall Pot 1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Mooodz Glory'</t>
+          <t>Phormium 'Flamingo'</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Hilmooglor'</t>
+          <t>Phormium 'Flamingo'</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest flowering; tolerates partial shade.</t>
+          <t>Full sun for strongest foliage colour; shelter from severe cold wind.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
+          <t>Water while establishing, then let the upper compost dry slightly; never leave the pot waterlogged.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
+          <t>Remove only damaged leaves at the base. Raise the pot for winter drainage and protect the crown during severe frost.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
+          <t>Evergreen, pink-striped sword-like leaves give year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Wall Pot 2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (2 plants)</t>
+          <t>Echinacea 'Mooodz Glory'</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Echinacea 'Hilmooglor'</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun for strongest flowering; tolerates partial shade.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist while establishing; never waterlog.</t>
+          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Use free-draining, preferably ericaceous compost. Trim lightly after flowering, never into bare wood.</t>
+          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and late-summer to autumn colour.</t>
+          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
         </is>
       </c>
     </row>
@@ -3898,32 +3898,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee' (2 plants)</t>
+          <t>Fuchsia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Fuchsia hybrid</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Bright shade to morning sun; shelter from harsh reflected afternoon heat.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist, particularly in windy weather.</t>
+          <t>Keep the basket compost evenly moist and freely drained.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods to extend the display.</t>
+          <t>Deadhead flowers and developing berries; pinch or shorten long bare shoots to keep the basket balanced.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with a pale picotee edge through the cool season.</t>
+          <t>Pendant flowers through the mild season; protect from frost if the plant is to be retained.</t>
         </is>
       </c>
     </row>
@@ -3935,32 +3935,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple' (2 plants)</t>
+          <t>Fern (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
+          <t>Fern — cultivar to confirm</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Shade to sun; avoid prolonged scorching sun on pale foliage.</t>
+          <t>Bright shade to partial shade; avoid hot, drying sun until the fern is identified.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared basket compost evenly moist and well drained.</t>
+          <t>Keep compost evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Trim trails to shape and keep stems clear of neighbouring crowns.</t>
+          <t>Remove damaged fronds at the base and protect the crown from prolonged winter wet. Retain a label or a close frond photograph for identification.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Evergreen variegated trails give structure through winter.</t>
+          <t>Foliage interest; hardiness and winter behaviour remain to be confirmed from the cultivar.</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Fire' (2 plants)</t>
+          <t>Lysimachia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Fire'</t>
+          <t>Lysimachia — cultivar to confirm</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3987,17 +3987,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but never saturated.</t>
+          <t>Keep compost evenly moist while establishing.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods regularly.</t>
+          <t>Trim trailing growth to shape and avoid letting it smother the retained plants.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Cool-season flowers provide autumn-to-spring colour.</t>
+          <t>Fresh foliage is expected to trail through the basket; exact cultivar and winter behaviour remain to be confirmed.</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Rose Surprise' (2 plants)</t>
+          <t>Chrysanthemum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Rose Surprise'</t>
+          <t>Chrysanthemum — cultivar to confirm</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4024,720 +4024,720 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but never saturated.</t>
+          <t>Keep compost moist but well drained; do not leave the basket standing wet.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods regularly.</t>
+          <t>Remove spent flowers and damaged leaves. Treat hardiness as unknown until a label confirms the cultivar.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Cool-season flowers provide autumn-to-spring colour.</t>
+          <t>Autumn flowers provide late colour; cultivar and overwintering potential are unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea</t>
+          <t>Cyclamen (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea macrophylla</t>
+          <t>Cyclamen — cultivar to confirm</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Morning sun, afternoon shade.</t>
+          <t>Bright, sheltered partial shade.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Thirsty — water well in dry spells.</t>
+          <t>Water the compost sparingly around the edge, avoiding a saturated crown.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
+          <t>Remove fading flowers and yellow leaves with a clean twist. Protect from hard frost unless a hardy cultivar is confirmed.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Mophead flowers July–Sept; bare in winter.</t>
+          <t>Cool-season flowers and foliage; cultivar and hardiness remain to be confirmed.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Lavandula angustifolia</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Drought-tolerant.</t>
+          <t>Keep compost lightly moist while establishing; never waterlog.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
+          <t>Use free-draining, preferably ericaceous compost. Trim lightly after flowering, never into bare wood.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Purple spikes June–Aug; aromatic year-round.</t>
+          <t>Evergreen foliage and late-summer to autumn colour.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Viola 'Rocky Purple Picotee' (2 plants)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Avoid waterlogged soil.</t>
+          <t>Keep compost evenly moist, particularly in windy weather.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
+          <t>Deadhead faded flowers and seed pods to extend the display.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
+          <t>Purple flowers with a pale picotee edge through the cool season.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Hedera helix 'Yellow Ripple' (2 plants)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
+          <t>Shade to sun; avoid prolonged scorching sun on pale foliage.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Let the soil drain between waterings.</t>
+          <t>Keep the shared basket compost evenly moist and well drained.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
+          <t>Trim trails to shape and keep stems clear of neighbouring crowns.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
+          <t>Evergreen variegated trails give structure through winter.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Pansy 'Fire' (2 plants)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Viola × wittrockiana 'Fire'</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi' (Horopito)</t>
+          <t>Pansy 'Rose Surprise' (2 plants)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi'</t>
+          <t>Viola × wittrockiana 'Rose Surprise'</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Hydrangea</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Hydrangea macrophylla</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
+          <t>Morning sun, afternoon shade.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
+          <t>Thirsty — water well in dry spells.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
+          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
+          <t>Mophead flowers July–Sept; bare in winter.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Climbing Rose 'Super Fairy'</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Helsufair'</t>
+          <t>Lavandula angustifolia</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sun to light partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base in dry spells, especially while establishing.</t>
+          <t>Drought-tolerant.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
+          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
+          <t>Purple spikes June–Aug; aromatic year-round.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Variegated Dogwood</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Cornus alba 'Elegantissima'</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
+          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
+          <t>Moderate while establishing. Avoid waterlogged soil.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
+          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
+          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Red Hot Poker</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Kniphofia</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering.</t>
+          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
+          <t>Moderate while establishing. Let the soil drain between waterings.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
+          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
+          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
+          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
+          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
+          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
+          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Rose (pink)</t>
+          <t>Hebe 'Kiwi' (Horopito)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Rosa — IDENTIFY</t>
+          <t>Hebe 'Kiwi'</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sun.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Prune late winter; deadhead through summer.</t>
+          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–Sept; bare winter.</t>
+          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Photinia (existing canopy)</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Photinia (cultivar to confirm)</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Water deeply only in prolonged dry periods once established.</t>
+          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
+          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
+          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>The Pilgrim</t>
+          <t>Cercis 'Eternal Flame'</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Auswalker'</t>
+          <t>Cercis canadensis 'Eternal Flame' ('Nc2016-2')</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
+          <t>Full sun in fertile, moisture-retentive but well-drained soil.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially while establishing.</t>
+          <t>Water deeply through dry spells for the first two growing seasons; do not leave the root zone waterlogged.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
+          <t>Keep a weed-free mulched circle, avoid hard pruning and stake only while the young tree establishes. Check leaves and stems for scale or stress before treating.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
+          <t>Glossy young foliage opens red and matures through orange and yellow tones; mature trees flower pink on bare stems in spring; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>The Generous Gardener</t>
+          <t>Climbing Rose 'Super Fairy'</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Ausdrawn'</t>
+          <t>Rosa 'Helsufair'</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
+          <t>Sun to light partial shade.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially in its first two years.</t>
+          <t>Deep water at the base in dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
+          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
+          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
+          <t>Variegated Dogwood</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
+          <t>Cornus alba 'Elegantissima'</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; foliage is darkest with good light.</t>
+          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
+          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
+          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
+          <t>Red Hot Poker</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
+          <t>Kniphofia</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; best foliage colour in brighter light.</t>
+          <t>Full sun for the strongest flowering.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
+          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
+          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Silvester'</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Sylvester'</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
+          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
+          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope'</t>
+          <t>Rose (pink)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
+          <t>Rosa — IDENTIFY</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade in a sheltered position.</t>
+          <t>Sun.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
+          <t>Prune late winter; deadhead through summer.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
+          <t>Flowers June–Sept; bare winter.</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4749,32 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Purple Gem</t>
+          <t>Photinia (existing canopy)</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
+          <t>Photinia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Shade to partial shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
+          <t>Water deeply only in prolonged dry periods once established.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
+          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
+          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
         </is>
       </c>
     </row>
@@ -4786,32 +4786,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>The Pilgrim</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Rosa 'Auswalker'</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
+          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
+          <t>Deep water at the base during dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
+          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
+          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Festuca 'Elijah Blue' (3 plants)</t>
+          <t>The Generous Gardener</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Festuca glauca 'Elijah Blue'</t>
+          <t>Rosa 'Ausdrawn'</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Water regularly during the first season; drought tolerant once established.</t>
+          <t>Deep water at the base during dry spells, especially in its first two years.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
+          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
+          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4860,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Pieris 'Polar Passion'</t>
+          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
+          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
+          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
+          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4897,32 +4897,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Dahlia 'Tampico'</t>
+          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
+          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Full sun, sheltered from strong wind.</t>
+          <t>Sun to partial shade; best foliage colour in brighter light.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
+          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
+          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Margaret's Memory'</t>
+          <t>Azalea japonica 'Silvester'</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Glandularia 'Margaret's Memory'</t>
+          <t>Rhododendron 'Sylvester'</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
+          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (2 plants)</t>
+          <t>Nemesia 'Lady Penelope'</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Full sun in an open position.</t>
+          <t>Full sun to light partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
+          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
+          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>A two-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
+          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
         </is>
       </c>
     </row>
@@ -5008,32 +5008,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Achillea</t>
+          <t>Purple Gem</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Achillea millefolium</t>
+          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
+          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
+          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
         </is>
       </c>
     </row>
@@ -5045,291 +5045,291 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Lotte'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Lotte'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
+          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
+          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Mexican Orange Blossom</t>
+          <t>Festuca 'Elijah Blue' (3 plants)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Choisya ternata 'Sundance'</t>
+          <t>Festuca glauca 'Elijah Blue'</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Sun for best colour.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Water regularly during the first season; drought tolerant once established.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering to shape. Low-care.</t>
+          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
+          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Shrub Rose (cultivar to confirm)</t>
+          <t>Pieris 'Polar Passion'</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Rosa (Shrub Group; cultivar to confirm)</t>
+          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
+          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
+          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
+          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
+          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Bay Tree</t>
+          <t>Dahlia 'Tampico'</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun, sheltered from strong wind.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
+          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
+          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
+          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Japanese Skimmia</t>
+          <t>Verbena 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica (cultivar and sex to confirm)</t>
+          <t>Glandularia 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
+          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
+          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
+          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Hardy Fuchsia (cultivar to confirm)</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
+          <t>Full sun in an open position.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
+          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
+          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
+          <t>A two-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Clematis (cultivar to confirm)</t>
+          <t>Achillea</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Clematis viticella (cultivar to confirm)</t>
+          <t>Achillea millefolium</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade, with a cool shaded root run.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
+          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Deciduous climber with abundant summer flowers on new growth.</t>
+          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Bloody Marie'</t>
+          <t>Azalea japonica 'Lotte'</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea paniculata 'Bloody Marie'</t>
+          <t>Rhododendron 'Lotte'</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
+          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -5341,32 +5341,32 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia 'Ascot Petite'</t>
+          <t>Mexican Orange Blossom</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia × martinii 'Ascot Petite'</t>
+          <t>Choisya ternata 'Sundance'</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a sheltered position.</t>
+          <t>Sun for best colour.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
+          <t>Light prune after flowering to shape. Low-care.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
+          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Flaming Silver</t>
+          <t>Shrub Rose (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Flaming Silver'</t>
+          <t>Rosa (Shrub Group; cultivar to confirm)</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
+          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
+          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
+          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
+          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Astrantia trio</t>
+          <t>Bay Tree</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Sun to light shade.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
+          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
+          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
+          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum 'Tom Thumb'</t>
+          <t>Japanese Skimmia</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
+          <t>Skimmia japonica (cultivar and sex to confirm)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
+          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
+          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
+          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
         </is>
       </c>
     </row>
@@ -5489,32 +5489,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Gaura 'Gaudi Red'</t>
+          <t>Hardy Fuchsia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
+          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
+          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
+          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
+          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
         </is>
       </c>
     </row>
@@ -5526,32 +5526,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Bell's Extra Special'</t>
+          <t>Clematis (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Erica carnea 'Bell's Extra Special'</t>
+          <t>Clematis viticella (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
+          <t>Sun to partial shade, with a cool shaded root run.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
+          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
+          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
+          <t>Deciduous climber with abundant summer flowers on new growth.</t>
         </is>
       </c>
     </row>
@@ -5563,32 +5563,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Tib'</t>
+          <t>Hydrangea 'Bloody Marie'</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Tib'</t>
+          <t>Hydrangea paniculata 'Bloody Marie'</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and the best flower display.</t>
+          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
+          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
+          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
+          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Bell Heather 'Providence' (2 plants)</t>
+          <t>Euphorbia 'Ascot Petite'</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Daboecia cantabrica 'Providence'</t>
+          <t>Euphorbia × martinii 'Ascot Petite'</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
+          <t>Full sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
+          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
+          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
+          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Leprechaun'</t>
+          <t>Flaming Silver</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Leprechaun'</t>
+          <t>Pieris japonica 'Flaming Silver'</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the brightest foliage colour.</t>
+          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
+          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
+          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
+          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
         </is>
       </c>
     </row>
@@ -5674,32 +5674,32 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Winter Chocolate'</t>
+          <t>Astrantia trio</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Winter Chocolate'</t>
+          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
+          <t>Sun to light shade.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
+          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
+          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
+          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
         </is>
       </c>
     </row>
@@ -5711,32 +5711,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee'</t>
+          <t>Pittosporum 'Tom Thumb'</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; do not allow the planting pocket to become waterlogged.</t>
+          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong the cool-season display.</t>
+          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with pale picotee margins through autumn, winter and spring.</t>
+          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma</t>
+          <t>Gaura 'Gaudi Red'</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma plumbaginoides</t>
+          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
+          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
+          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
+          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5785,32 +5785,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Heather 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Erica carnea 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
+          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
+          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
+          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
+          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bluebell Creeper</t>
+          <t>Heather 'Tib'</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
+          <t>Calluna vulgaris 'Tib'</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered position.</t>
+          <t>Full sun for compact growth and the best flower display.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
+          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
+          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
+          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
         </is>
       </c>
     </row>
@@ -5859,32 +5859,32 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Rhubarb and Custard'</t>
+          <t>Bell Heather 'Providence' (2 plants)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
+          <t>Daboecia cantabrica 'Providence'</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered spot.</t>
+          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
+          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
+          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
+          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
         </is>
       </c>
     </row>
@@ -5896,32 +5896,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Salgoon Lake Blueberry'</t>
+          <t>Heather 'Leprechaun'</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
+          <t>Calluna vulgaris 'Leprechaun'</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun for the brightest foliage colour.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
+          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
+          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
+          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
         </is>
       </c>
     </row>
@@ -5933,740 +5933,1184 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Fern 'Jurassic Gold'</t>
+          <t>Heather 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
+          <t>Calluna vulgaris 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Full shade in a sheltered position.</t>
+          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
+          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
+          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
+          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Front Stone Trough</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Viola 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Part to full shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; never bone-dry in the trough.</t>
+          <t>Keep evenly moist while establishing; do not allow the planting pocket to become waterlogged.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Watch for slugs/snails. Divide clumps in spring.</t>
+          <t>Deadhead faded flowers and seed pods regularly to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Fresh leaves spring; dies back over winter.</t>
+          <t>Purple flowers with pale picotee margins through autumn, winter and spring.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Front Box Hedge</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Wall Cotoneaster (species to confirm)</t>
+          <t>Ceratostigma</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Cotoneaster (species to confirm)</t>
+          <t>Ceratostigma plumbaginoides</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Sun to part shade.</t>
+          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
+          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
+          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
+          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Mixed Pot</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Mixed seasonal planting — contents to confirm</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
+          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
+          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
+          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
+          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia Pot</t>
+          <t>Bluebell Creeper</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia cultivars — identities to confirm</t>
+          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
+          <t>Full sun to partial shade in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
+          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
+          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
+          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Hebe 'Rhubarb and Custard'</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Water well in dry spells while fruiting.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Blossom April–May; fruit late summer–autumn.</t>
+          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Damson Tree</t>
+          <t>Salvia 'Salgoon Lake Blueberry'</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable blossom and fruit ripening.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Front Gate Tree</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Weeping Crab Apple (cultivar to confirm)</t>
+          <t>Fern 'Jurassic Gold'</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+          <t>Full shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Kentia Palm</t>
+          <t>Front Stone Trough</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Kentia Palm — assumed</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Howea forsteriana</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+          <t>Part to full shade.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+          <t>Keep moist; never bone-dry in the trough.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+          <t>Watch for slugs/snails. Divide clumps in spring.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+          <t>Fresh leaves spring; dies back over winter.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>House · Kitchen / Dining · ‘Gioia’ Fern</t>
+          <t>Front Box Hedge</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Bird’s Nest Fern ‘Gioia’</t>
+          <t>Wall Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Asplenium antiquum ‘Gioia’</t>
+          <t>Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
+          <t>Sun to part shade.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
+          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
+          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
+          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Staghorn Fern</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Staghorn Fern</t>
+          <t>Hedera helix 'Yellow Ripple' · Pot 1</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Platycerium bifurcatum</t>
+          <t>Hedera helix 'Yellow Ripple'</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+          <t>Keep compost evenly moist and well drained while establishing.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+          <t>Trim trails to shape and keep stems clear of the neighbouring Skimmia and Pansies.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+          <t>Evergreen variegated foliage provides year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Spider Plant ‘Vittatum’ — assumed</t>
+          <t>Skimmia 'Double Diamond'</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Chlorophytum comosum ‘Vittatum’</t>
+          <t>Skimmia 'Double Diamond'</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light is ideal; it tolerates lower light but direct hot sun can scorch the striped leaves.</t>
+          <t>Partial shade to shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Allow the compost surface to begin drying, then water thoroughly and let the shared container drain fully.</t>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Trim only spent stems or badly damaged leaves, feed lightly during active growth and root the hanging plantlets if wanted.</t>
+          <t>Use ericaceous compost, keep the crown clear and protect the pot from winter waterlogging.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Evergreen striped foliage and hanging plantlets are the year-round display; growth slows in winter.</t>
+          <t>Evergreen foliage gives structure; flower and berry details will be observed as the plant establishes.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Parlour Palm — assumed</t>
+          <t>Pansy 'Fire Red' · Pot 1</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Chamaedorea elegans</t>
+          <t>Viola × wittrockiana 'Fire Red'</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light or light shade; protect the fine leaflets from strong direct sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Check below the surface before watering; keep lightly moist in growth but never leave the shared planter waterlogged.</t>
+          <t>Keep compost evenly moist without saturation.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Keep warm, remove only fully brown fronds at the base and feed monthly at low strength in spring and summer.</t>
+          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Evergreen fine-textured fronds provide the display throughout the year; growth is slowest in winter.</t>
+          <t>Red flowers provide autumn-to-spring container colour.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Arrowhead Vine — assumed</t>
+          <t>Hedera helix 'Yellow Ripple' · Pot 2</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Syngonium podophyllum</t>
+          <t>Hedera helix 'Yellow Ripple'</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; keep the leaves out of strong direct sun through the glass.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Keep lightly moist during active growth, allowing the surface to begin drying; water more sparingly in winter.</t>
+          <t>Keep compost evenly moist and well drained while establishing.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Guide or trim lengthening stems in spring, feed during active growth and wear gloves if pruning because the sap is irritating.</t>
+          <t>Trim trails to shape and keep stems clear of the Gaultheria and Pansies.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Evergreen juvenile arrow-shaped leaves become more divided as stems mature; indoor flowering is uncommon.</t>
+          <t>Evergreen variegated foliage provides year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Gaultheria (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Gaultheria — cultivar to confirm</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Partial shade to shade.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Keep compost evenly moist and acidic, never waterlogged.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Use ericaceous compost and rainwater where possible. Retain a label or berry and foliage close-up before assigning a cultivar.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+          <t>Evergreen foliage and possible autumn berries; cultivar is not yet confirmed.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Pansy 'Fire Red' · Pot 2</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Viola × wittrockiana 'Fire Red'</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+          <t>Keep compost evenly moist without saturation.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
+          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
+          <t>Red flowers provide autumn-to-spring container colour.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Front Strawberry Tree</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun in a sheltered, well-drained position.</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost evenly moist but well drained.</t>
+          <t>Water regularly through the first two years, increasing in hot or dry weather; avoid waterlogging.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+          <t>Keep a clear, mulched root area while it establishes. Prune only to remove damaged or crossing growth, and stake a young standard tree until secure.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with pale picotee margins through the cool season.</t>
+          <t>Evergreen foliage; white urn-shaped autumn flowers and ornamental red fruits can appear together on established plants.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Water well in dry spells while fruiting.</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Damson Tree</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>Front Gate Tree</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>House · Hallway · Kentia Palm</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Kentia Palm — assumed</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Howea forsteriana</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>House · Kitchen / Dining · ‘Gioia’ Fern</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Bird’s Nest Fern ‘Gioia’</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Asplenium antiquum ‘Gioia’</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>House · Hallway · Staghorn Fern</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Staghorn Fern</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Platycerium bifurcatum</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Spider Plant ‘Vittatum’ — assumed</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Chlorophytum comosum ‘Vittatum’</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Bright indirect light is ideal; it tolerates lower light but direct hot sun can scorch the striped leaves.</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Allow the compost surface to begin drying, then water thoroughly and let the shared container drain fully.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Trim only spent stems or badly damaged leaves, feed lightly during active growth and root the hanging plantlets if wanted.</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen striped foliage and hanging plantlets are the year-round display; growth slows in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Parlour Palm — assumed</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Chamaedorea elegans</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Bright indirect light or light shade; protect the fine leaflets from strong direct sun.</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Check below the surface before watering; keep lightly moist in growth but never leave the shared planter waterlogged.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Keep warm, remove only fully brown fronds at the base and feed monthly at low strength in spring and summer.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen fine-textured fronds provide the display throughout the year; growth is slowest in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Arrowhead Vine — assumed</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Syngonium podophyllum</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Bright indirect light; keep the leaves out of strong direct sun through the glass.</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Keep lightly moist during active growth, allowing the surface to begin drying; water more sparingly in winter.</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Guide or trim lengthening stems in spring, feed during active growth and wear gloves if pruning because the sap is irritating.</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen juvenile arrow-shaped leaves become more divided as stems mature; indoor flowering is uncommon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Cleopatra'</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Antarctica'</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Antarctica'</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shared compost evenly moist but well drained.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Purple flowers with pale picotee margins through the cool season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G168"/>
+  <autoFilter ref="A1:G180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -3893,7 +3893,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Hanging Basket 3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Hanging Basket 3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Hanging Basket 3</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Hanging Basket 3</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Hanging Basket 3</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$182</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6303,32 +6303,32 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple' · Pot 1</t>
+          <t>Mixed Pot</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple'</t>
+          <t>Mixed seasonal planting — contents to confirm</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and well drained while establishing.</t>
+          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Trim trails to shape and keep stems clear of the neighbouring Skimmia and Pansies.</t>
+          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Evergreen variegated foliage provides year-round structure.</t>
+          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
         </is>
       </c>
     </row>
@@ -6340,49 +6340,49 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Double Diamond'</t>
+          <t>Fuchsia Pot</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Double Diamond'</t>
+          <t>Fuchsia cultivars — identities to confirm</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade in a sheltered position.</t>
+          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Use ericaceous compost, keep the crown clear and protect the pot from winter waterlogging.</t>
+          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage gives structure; flower and berry details will be observed as the plant establishes.</t>
+          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Fire Red' · Pot 1</t>
+          <t>Hedera helix 'Yellow Ripple' · Pot 1</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Fire Red'</t>
+          <t>Hedera helix 'Yellow Ripple'</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -6392,108 +6392,108 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist without saturation.</t>
+          <t>Keep compost evenly moist and well drained while establishing.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
+          <t>Trim trails to shape and keep stems clear of the neighbouring Skimmia and Pansies.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Red flowers provide autumn-to-spring container colour.</t>
+          <t>Evergreen variegated foliage provides year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple' · Pot 2</t>
+          <t>Skimmia 'Double Diamond'</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple'</t>
+          <t>Skimmia 'Double Diamond'</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Partial shade to shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and well drained while establishing.</t>
+          <t>Keep compost evenly moist and freely drained.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Trim trails to shape and keep stems clear of the Gaultheria and Pansies.</t>
+          <t>Use ordinary peat-free container compost, keep the crown clear and protect the pot from winter waterlogging.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Evergreen variegated foliage provides year-round structure.</t>
+          <t>Evergreen foliage gives structure; flower and berry details will be observed as the plant establishes.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Gaultheria (cultivar to confirm)</t>
+          <t>Pansy 'Fire Red' · Pot 1</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Gaultheria — cultivar to confirm</t>
+          <t>Viola × wittrockiana 'Fire Red'</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and acidic, never waterlogged.</t>
+          <t>Keep compost evenly moist without saturation.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Use ericaceous compost and rainwater where possible. Retain a label or berry and foliage close-up before assigning a cultivar.</t>
+          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and possible autumn berries; cultivar is not yet confirmed.</t>
+          <t>Red flowers provide autumn-to-spring container colour.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Fire Red' · Pot 2</t>
+          <t>Hedera helix 'Yellow Ripple' · Pot 2</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Fire Red'</t>
+          <t>Hedera helix 'Yellow Ripple'</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -6503,461 +6503,461 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist without saturation.</t>
+          <t>Keep compost evenly moist and well drained while establishing.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
+          <t>Trim trails to shape and keep stems clear of the Gaultheria and Pansies.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Red flowers provide autumn-to-spring container colour.</t>
+          <t>Evergreen variegated foliage provides year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Front Strawberry Tree</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Arbutus unedo</t>
+          <t>Gaultheria (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Arbutus unedo</t>
+          <t>Gaultheria — cultivar to confirm</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a sheltered, well-drained position.</t>
+          <t>Partial shade to shade.</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Water regularly through the first two years, increasing in hot or dry weather; avoid waterlogging.</t>
+          <t>Keep compost evenly moist and acidic, never waterlogged.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Keep a clear, mulched root area while it establishes. Prune only to remove damaged or crossing growth, and stake a young standard tree until secure.</t>
+          <t>Use ericaceous compost and rainwater where possible. Retain a label or berry and foliage close-up before assigning a cultivar.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage; white urn-shaped autumn flowers and ornamental red fruits can appear together on established plants.</t>
+          <t>Evergreen foliage and possible autumn berries; cultivar is not yet confirmed.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Stairs Pots</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Pansy 'Fire Red' · Pot 2</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Viola × wittrockiana 'Fire Red'</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Water well in dry spells while fruiting.</t>
+          <t>Keep compost evenly moist without saturation.</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+          <t>Remove faded flowers and seed pods to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Blossom April–May; fruit late summer–autumn.</t>
+          <t>Red flowers provide autumn-to-spring container colour.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Strawberry Tree</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Damson Tree</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable blossom and fruit ripening.</t>
+          <t>Full sun in a sheltered, well-drained position.</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+          <t>Water regularly through the first two years, increasing in hot or dry weather; avoid waterlogging.</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+          <t>Keep a clear, mulched root area while it establishes. Prune only to remove damaged or crossing growth, and stake a young standard tree until secure.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+          <t>Evergreen foliage; white urn-shaped autumn flowers and ornamental red fruits can appear together on established plants.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Front Gate Tree</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Weeping Crab Apple (cultivar to confirm)</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+          <t>Water well in dry spells while fruiting.</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Kentia Palm</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Kentia Palm — assumed</t>
+          <t>Damson Tree</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Howea forsteriana</t>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>House · Kitchen / Dining · ‘Gioia’ Fern</t>
+          <t>Front Gate Tree</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Bird’s Nest Fern ‘Gioia’</t>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Asplenium antiquum ‘Gioia’</t>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Staghorn Fern</t>
+          <t>House · Hallway · Kentia Palm</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Staghorn Fern</t>
+          <t>Kentia Palm — assumed</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Platycerium bifurcatum</t>
+          <t>Howea forsteriana</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
+          <t>House · Kitchen / Dining · ‘Gioia’ Fern</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Spider Plant ‘Vittatum’ — assumed</t>
+          <t>Bird’s Nest Fern ‘Gioia’</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Chlorophytum comosum ‘Vittatum’</t>
+          <t>Asplenium antiquum ‘Gioia’</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light is ideal; it tolerates lower light but direct hot sun can scorch the striped leaves.</t>
+          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Allow the compost surface to begin drying, then water thoroughly and let the shared container drain fully.</t>
+          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Trim only spent stems or badly damaged leaves, feed lightly during active growth and root the hanging plantlets if wanted.</t>
+          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Evergreen striped foliage and hanging plantlets are the year-round display; growth slows in winter.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
+          <t>House · Hallway · Staghorn Fern</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Parlour Palm — assumed</t>
+          <t>Staghorn Fern</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Chamaedorea elegans</t>
+          <t>Platycerium bifurcatum</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light or light shade; protect the fine leaflets from strong direct sun.</t>
+          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Check below the surface before watering; keep lightly moist in growth but never leave the shared planter waterlogged.</t>
+          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Keep warm, remove only fully brown fronds at the base and feed monthly at low strength in spring and summer.</t>
+          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Evergreen fine-textured fronds provide the display throughout the year; growth is slowest in winter.</t>
+          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
+          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Arrowhead Vine — assumed</t>
+          <t>Spider Plant ‘Vittatum’ — assumed</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Syngonium podophyllum</t>
+          <t>Chlorophytum comosum ‘Vittatum’</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; keep the leaves out of strong direct sun through the glass.</t>
+          <t>Bright indirect light is ideal; it tolerates lower light but direct hot sun can scorch the striped leaves.</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Keep lightly moist during active growth, allowing the surface to begin drying; water more sparingly in winter.</t>
+          <t>Allow the compost surface to begin drying, then water thoroughly and let the shared container drain fully.</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Guide or trim lengthening stems in spring, feed during active growth and wear gloves if pruning because the sap is irritating.</t>
+          <t>Trim only spent stems or badly damaged leaves, feed lightly during active growth and root the hanging plantlets if wanted.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Evergreen juvenile arrow-shaped leaves become more divided as stems mature; indoor flowering is uncommon.</t>
+          <t>Evergreen striped foliage and hanging plantlets are the year-round display; growth slows in winter.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Parlour Palm — assumed</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Chamaedorea elegans</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Bright indirect light or light shade; protect the fine leaflets from strong direct sun.</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Check below the surface before watering; keep lightly moist in growth but never leave the shared planter waterlogged.</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Keep warm, remove only fully brown fronds at the base and feed monthly at low strength in spring and summer.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+          <t>Evergreen fine-textured fronds provide the display throughout the year; growth is slowest in winter.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Arrowhead Vine — assumed</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Syngonium podophyllum</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Bright indirect light; keep the leaves out of strong direct sun through the glass.</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+          <t>Keep lightly moist during active growth, allowing the surface to begin drying; water more sparingly in winter.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
+          <t>Guide or trim lengthening stems in spring, feed during active growth and wear gloves if pruning because the sap is irritating.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
+          <t>Evergreen juvenile arrow-shaped leaves become more divided as stems mature; indoor flowering is uncommon.</t>
         </is>
       </c>
     </row>
@@ -6969,148 +6969,222 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost evenly moist but well drained.</t>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with pale picotee margins through the cool season.</t>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Keep the shared compost evenly moist but well drained.</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>Purple flowers with pale picotee margins through the cool season.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G180"/>
+  <autoFilter ref="A1:G182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$L$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$L$187</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13419,71 +13419,75 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
+          <t>House · Sitting Room · Nicola’s Mixed Planter</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Spider Plant ‘Vittatum’ — assumed</t>
+          <t>Nicola’s Mixed Planter — identities assumed</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Chlorophytum comosum ‘Vittatum’</t>
+          <t>Chlorophytum · Chamaedorea · Syngonium</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect. Tolerates lower light; hot direct sun can mark the foliage</t>
+          <t>Bright indirect. Filter strong sitting-room window sun and keep smaller companions visible</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface begin drying, then soak and drain the shared pot</t>
+          <t>Moderate · shared root ball. Test below the surface in several places, water evenly when needed and drain fully</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Keep the window light filtered: Bright indirect light maintains clean variegation. The sitting-room window is useful light, but move the planter back or filter the glass if strong direct sun begins bleaching or scorching the leaves.
-Water the shared root ball, then drain: Use the compost, not a calendar, to decide. Test below the surface in several places because the large clump can hide dry pockets. Water thoroughly only when the surface is beginning to dry and never leave runoff in the outer container.
-Choose which plantlets to keep: The long runners are healthy propagation growth. Root wanted plantlets in small pots while still attached, then cut the connecting stem. Remove spent flowering stems only when no more plantlets are wanted.
-Review crowding in spring: Three vigorous species are sharing one root space. If water runs straight through, the centre stays dry or growth weakens, slide out the root ball in spring and decide whether to divide the Spider Plant or separate the three species.</t>
+          <t>Give all three plants filtered light: Bright indirect light suits the shared display. Filter harsh glass sun and guide the dominant Spider Plant leaves away from the palm’s small crown and the vine. Rotate the pot for balanced growth.
+Water the pot once, checking several pockets: One container needs one moisture decision. Test around the palm, vine and pot edge. Water evenly when the surface begins to dry, keeping the active-growth root ball lightly moist but never saturated. Empty runoff and lengthen watering intervals in winter.
+Trim each component appropriately: Keep the mixed canopy open without cutting healthy palm growth. Root or remove selected Spider Plant plantlets; remove only fully brown palm fronds at their bases. Guide or shorten long Arrowhead Vine stems in spring, wearing gloves and keeping cuttings out of reach.
+Review crowding during spring growth: The Spider Plant’s fleshy roots can crowd its companions. If water races through, dry pockets persist or smaller plants weaken, inspect the shared root ball in spring. Divide or separate only if congestion warrants it; feed modestly during active growth using the product instructions.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Spring: Look for fresh striped leaves and plantlets, feed lightly and check whether the Spider Plant's fleshy roots are displacing its two pot companions.
-Summer: Keep the striped rosette in filtered light, water the shared pot only after checking depth and trim brown tips without cutting healthy green tissue.
-Autumn: Remove spent plantlet stems and stop feeding as growth slows, noting whether its vigorous roots are making separation necessary.
-Winter: Maximise gentle light for the white stripe, water sparingly and keep leaf tips away from the sitting-room radiator.</t>
+          <t>Spring: Inspect the shared root ball for crowding as fresh growth starts; manage Spider Plant plantlets, retain green palm fronds and guide or shorten vine stems with gloves.
+Summer: Filter strong window sun, test moisture near all three plants, rotate the planter and inspect palm fronds and vine leaf undersides for pests.
+Autumn: Stop routine feeding as growth slows, remove spent runners and fully brown foliage, and keep the complete planter clear of cold window draughts.
+Winter: Give the whole pot gentle daylight and steady warmth; water less often after checking depth and keep leaves away from radiator air.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>The dominant cascading plant in Nicola’s mixed gift pot is a Spider Plant. Its creamy central leaf stripe, green margins and long runners carrying young plantlets closely fit Chlorophytum comosum ‘Vittatum’; the cultivar remains visibly assumed because no label has been retained.</t>
+          <t>One large sitting-room pot gifted by Nicola, Katie’s mum. An arching Spider Plant ‘Vittatum’, upright Parlour Palm and smaller Arrowhead Vine grow together in the same container. These photo-based identities remain assumed without retained labels; the planter is recorded and watered as one unit.</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Habit: Arching clump. Long striped leaves form a dense fountain over the shared planter
-Light: Bright indirect. Tolerates lower light; hot direct sun can mark the foliage
-Water: Moderate. Let the surface begin drying, then soak and drain the shared pot
-Plantlets: Many runners. Young plants can be rooted while attached or removed once rooted
-Identity: ‘Vittatum’ assumed. Central creamy stripes and especially long arching leaves support the best fit
-Pet safety: Non-toxic listed. ASPCA listing for Chlorophytum
-Care priority: Keep runners off the smaller companions. Trim or pot selected spider plantlets before the vigorous arching growth shades the shared planter's palm and vine.</t>
+          <t>Contents: Three plants · one pot. Assumed Spider Plant ‘Vittatum’, Parlour Palm and Arrowhead Vine
+Light: Bright indirect. Filter strong sitting-room window sun and keep smaller companions visible
+Water: Moderate · shared root ball. Test below the surface in several places, water evenly when needed and drain fully
+Temperature: Warm indoor position. Protect the shared display from cold glass, draughts and radiator heat
+Habit: Arching, upright and climbing. Spider Plant runners surround fine palm fronds and juvenile arrow-shaped vine leaves
+Safety: Contains an irritant vine. Treat the whole shared planter as harmful if eaten because of the Arrowhead Vine
+Care priority: Check the whole mixed planter. Test moisture near all three plants, keep the palm and vine clear of Spider Plant runners and handle the Arrowhead Vine with gloves.</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Species confidence is high from the diagnostic runners and striped leaves. The central stripe and long arching habit make ‘Vittatum’ the leading cultivar, but it remains assumed without a retained label. Nicola, Katie’s mum, gave the complete three-plant pot to Oak Lodge.</t>
+          <t>Nicola, Katie’s mum, gave the complete planter to Oak Lodge. Central creamy stripes and runners support Chlorophytum comosum ‘Vittatum’; fine pinnate fronds support Chamaedorea elegans; arrow-shaped leaves and a climbing stem support Syngonium podophyllum. All component identities remain visibly assumed. Brad confirmed in October 2026 that they should be recorded together as one pot.</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/67933/chlorophytum-comosum-vittatum-v/details
-https://www.rhs.org.uk/plants/spider-plants/growing-guide
-https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/chlorophytum</t>
+          <t>https://www.rhs.org.uk/plants/spider-plants/growing-guide
+https://www.rhs.org.uk/plants/67933/chlorophytum-comosum-vittatum-v/details
+https://www.rhs.org.uk/plants/chamaedorea/growing-guide
+https://www.rhs.org.uk/plants/17899/syngonium-podophyllum/details
+https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/chlorophytum
+https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/chamaedorea
+https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/arrow-head-vine</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -13495,188 +13499,37 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Parlour Palm — assumed</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Chamaedorea elegans</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Indirect or light shade. Forest-understorey foliage scorches in strong direct sun</t>
+          <t>Partial or full shade. Shelter from strong sun and drying wind</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Moist but free-draining in growth; less water in winter</t>
+          <t>Avoid a dry root ball. Shade and reliable drainage matter; yellowing alone does not mean iron deficiency.</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Shelter the fine fronds from sun: Bright indirect light or light shade suits this understorey palm. Direct summer sun through the sitting-room glass can scorch or bleach the leaflets. Rotate the shared planter periodically for balanced light.
-Avoid permanent wetness: The palm likes regular moisture with air around its roots. Check the shared root ball before watering, soak evenly when it has begun to dry and empty all runoff. Reduce the frequency as winter growth slows.
-Keep old fronds until fully brown: Remove only finished growth at the base. Do not cut green leaflet tips into a tidy shape. Remove a frond cleanly at its base only after it has become fully brown.
-Feed and repot gently: Slow growth needs modest feeding and infrequent disturbance. Apply a balanced liquid feed monthly during spring and summer. Review the whole mixed root ball in spring if crowding or uneven drying becomes a problem.</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Spring: Watch for a new palm spear before beginning weak feed, and inspect the shared planter for crowding around the Palm's fine roots.
-Summer: Keep the fronds in bright filtered light, rotate the shared pot for even growth and check for spider mite in dry weather.
-Autumn: Stop feeding, remove only fully brown fronds at the base and protect the delicate leaflets from cold window draughts.
-Winter: Maintain steady room temperature and modest humidity, watering only after the shared compost has partly dried below the surface.</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>The upright plant rising through Nicola’s mixed gift pot is a Parlour Palm. Its slender clustered stems and compact pinnate fronds with many narrow leaflets strongly fit Chamaedorea elegans; the photo-based identification remains visibly assumed until a label is found.</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>Indoor size: Usually 30–60cm. Slow growing indoors, though old plants can eventually become larger
-Light: Indirect or light shade. Forest-understorey foliage scorches in strong direct sun
-Water: Moderate. Moist but free-draining in growth; less water in winter
-Temperature: Warm room. RHS recommends roughly 10–27°C, with stronger growth around 20–27°C
-Identity: Chamaedorea elegans. Fine pinnate fronds and slender stems support a high-confidence photo identification
-Pet safety: Non-toxic listed. ASPCA listing for Chamaedorea elegans
-Care priority: Expose the palm's small crown to light. Guide Spider Plant leaves away from the palm and inspect its fine fronds for mites in dry room air.</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>The fine pinnate fronds, numerous narrow leaflets and slender clustered stems make Parlour palm a high-confidence best fit, retained as assumed without a label. Nicola, Katie’s mum, gave the complete three-plant pot to Oak Lodge.</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rhs.org.uk/plants/chamaedorea/growing-guide
-https://www.rhs.org.uk/plants/29185/chamaedorea-elegans/details
-https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/chamaedorea</t>
-        </is>
-      </c>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>house-sitting-mixed-parlour-palm</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>Arrowhead Vine — assumed</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Syngonium podophyllum</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>Bright indirect. Green forms tolerate partial shade; strong direct sun can scorch</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Lightly moist. Water freely in active growth, more sparingly in winter, always with drainage</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>Keep it bright without harsh sun: Filtered window light maintains compact leafy growth. The larger Spider Plant may shade it heavily, so watch new growth for stretching while also preventing direct sun through the glass.
-Balance moisture across the shared pot: This vine prefers slightly steadier moisture than its companions. Test the compost around the vine as well as at the pot edge. Water the whole container when needed, drain fully and reduce watering in winter.
-Guide or shorten long stems: Arrowhead Vine naturally becomes a climber. Add a small support or trim leggy stems in spring. Wear gloves, keep sap away from eyes and wash tools and hands after pruning.
-Keep away from pets and children: Every part should be treated as harmful if chewed. Place the shared planter and any cuttings out of reach. Seek veterinary or medical advice promptly after suspected ingestion or significant sap exposure.</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Spring: Pinch the Arrowhead Vine above a node to encourage a compact shoot and begin light feeding only when new arrow-shaped leaves open.
-Summer: Guide or trim the fastest vine so it does not climb through the Palm, and check undersides of tender leaves for pests.
-Autumn: Stop feeding, remove yellow leaves at their petioles and decide whether the increasingly vining habit still suits the shared planter.
-Winter: Give the Arrowhead Vine bright indirect light, protect it from cold glass and allow the upper shared compost to dry slightly between checks.</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>The smaller arrow-leaved plant tucked beneath the Spider Plant is an Arrowhead Vine. Its juvenile sagittate leaves, pale midrib and climbing stem strongly support Syngonium podophyllum. No cultivar can be resolved from these photographs, and the species remains visibly assumed until labelled.</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>Habit: Climbing vine. Compact while young, then lengthens and can be guided or allowed to trail
-Light: Bright indirect. Green forms tolerate partial shade; strong direct sun can scorch
-Water: Lightly moist. Water freely in active growth, more sparingly in winter, always with drainage
-Temperature: Above 15°C. RHS rates it H1A for warm indoor conditions
-Identity: Species assumed. Juvenile arrow-shaped leaves and climbing stem support Syngonium podophyllum
-Safety: Oxalate irritant. Harmful if eaten and irritating to skin and eyes
-Care priority: Keep the vine accessible and out of reach. Trim climbing stems before they disappear through the palm, and keep this irritant plant away from pets and children.</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>Juvenile arrow-shaped leaves, pale venation and a climbing stem make Syngonium podophyllum a high-confidence best fit, but the species remains assumed and no cultivar is claimed. Nicola, Katie’s mum, gave the complete three-plant pot to Oak Lodge.</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rhs.org.uk/plants/17899/syngonium-podophyllum/details
-https://www.aspca.org/pet-care/aspca-poison-control/toxic-and-non-toxic-plants/arrow-head-vine</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="inlineStr">
-        <is>
-          <t>house-sitting-mixed-arrowhead-vine</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia Pot</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia 'Cleopatra'</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Partial or full shade. Shelter from strong sun and drying wind</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Avoid a dry root ball. Shade and reliable drainage matter; yellowing alone does not mean iron deficiency.</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Shade the Skimmia's roots: Keep moisture steady without standing water. Skimmias do not require ericaceous compost. Check exposure, dryness and drainage before trying to correct yellow leaves with iron or acidifying products.
 Preserve flowers and possible berries: Prune only wayward or damaged shoots, usually in spring. Heavy clipping removes flower buds. Female forms generally need a nearby male to set fruit; two female plants do not supply that pollen.
 Check pollination before expecting berries: For this Oak Lodge specimen Cleopatra shares the pot with Antarctica; do not assume the second Skimmia supplies compatible male flowers.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>Spring: Use rainwater where practical, feed with an ericaceous product after flowering and leave pollinated flower clusters intact for berries.
 Summer: Keep evenly moist in warm weather, checking beneath the ivy before watering.
@@ -13684,12 +13537,12 @@
 Winter: Keep drainage open and protect the decorative container during prolonged hard frost.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Cleopatra forms one of the evergreen centres of the Skimmia Pot, with glossy foliage and fragrant pale spring flowers. This female selection can carry red berries when compatible pollen is available; sharing a pot with another female does not provide it. Shade, an evenly moist root ball and drainage matter more than acidity: Skimmias do not require ericaceous compost.</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Size: About 0.5–1m. Compact rounded shrub suited to a large pot
 Position: Partial or full shade. Shelter from strong sun and drying wind
@@ -13701,57 +13554,57 @@
 Care priority: Check pollination before expecting berries. Cleopatra shares the pot with Antarctica; do not assume the second Skimmia supplies compatible male flowers.</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>The supplied garden record confirms Cleopatra; the registered cultivar epithet ‘Snep24’ and female berry-bearing habit come from the cultivar reference.</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/skimmia/growing-guide
 https://plantariumgroendirekt.nl/nieuwigheden-en/skimmia-japonica-snep24-cleopatra/?lang=en</t>
         </is>
       </c>
-      <c r="L179" s="2" t="inlineStr">
+      <c r="L177" s="2" t="inlineStr">
         <is>
           <t>lobeliapot-skimmia-cleopatra</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Skimmia Pot</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Partial shade. Sheltered shade reduces yellowing caused by hot dry exposure.</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Avoid a dry root ball. Shade and reliable drainage matter; yellowing alone does not mean iron deficiency.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Shade the Skimmia's roots: Keep moisture steady without standing water. Skimmias do not require ericaceous compost. Check exposure, dryness and drainage before trying to correct yellow leaves with iron or acidifying products.
 Preserve flowers and possible berries: Prune only wayward or damaged shoots, usually in spring. Heavy clipping removes flower buds. Female forms generally need a nearby male to set fruit; two female plants do not supply that pollen.
 Record Antarctica's flowers and fruit: For this Oak Lodge specimen Retain its separate label and observe the berry colour rather than copying Cleopatra's red-fruit description.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>Spring: Enjoy the fragrant flower clusters, remove frost-burned leaves individually and top-dress with fresh peat-free compost without covering the stem bases.
 Summer: Keep this evergreen pot evenly moist in hot weather and sheltered from harsh midday sun; do not shear off the developing berry clusters.
@@ -13759,12 +13612,12 @@
 Winter: Move the pot out of drying wind, raise it on feet and water only on frost-free days when the compost below the surface is genuinely dry.</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Antarctica is the second labelled Skimmia in the blue pot, sharing its root space with Cleopatra and three Rocky Purple Picotee Violas. Its compact evergreen framework gives year-round structure, while the spring flowers and any later fruit should be recorded separately from Cleopatra. Protect the root ball from drying and avoid assuming that pale foliage needs acidifying treatment.</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Size: Compact shrub. Cultivar dimensions need verification; pot size is not a permanent height limit.
 Position: Partial shade. Sheltered shade reduces yellowing caused by hot dry exposure.
@@ -13776,57 +13629,57 @@
 Care priority: Record Antarctica's flowers and fruit. Retain its separate label and observe the berry colour rather than copying Cleopatra's red-fruit description.</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>The supplied September update and photographs record this plant's identity and position.</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/skimmia/growing-guide
 https://www.rhs.org.uk/plants/364299/skimmia-japonica-antarctica/details</t>
         </is>
       </c>
-      <c r="L180" s="2" t="inlineStr">
+      <c r="L178" s="2" t="inlineStr">
         <is>
           <t>lobeliapot-skimmia-antarctica</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Skimmia Pot</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sun to partial shade. Keep the low flowers open to light beneath the two Skimmias.</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Moist, with free drainage. Small Viola and pansy roots dry quickly; cool, saturated compost can rot their crowns.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Remove flowers and seed capsules: Pinch each spent stem back to a leaf joint. Clear rain-damaged blooms promptly to limit grey mould. A light feed during growth helps sustain flowers in a container.
 Let cool weather set the pace: Expect pauses during hard frost or summer heat. Trim stretched stems to leafy growth if the crown is sound. Give light shade in hot weather and avoid burying small crowns under fallen leaves.
 Check all three low crowns: For this Oak Lodge specimen Keep the three Rocky Purple Picotee plants clear of fallen Skimmia leaves and inspect each small root plug.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>Spring: Deadhead back to a leaf joint, trim winter-scorched edges and give a light feed once fresh buds begin to move.
 Summer: Keep spent flowers and seed capsules removed; if heat stops flowering, shade the pot in the afternoon and expect a cooler-weather recovery.
@@ -13834,12 +13687,12 @@
 Winter: Pick off collapsed petals before botrytis spreads and protect the small root ball from alternating waterlogging and hard frost.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Three Rocky Purple Picotee Violas form a low purple-and-pale-edged flowering layer beneath the two Skimmias. Their cool-season display can pause in hard frost or summer heat. Each little crown needs light, airflow and reliable moisture, with spent flower stems and seed capsules removed before the shared pot becomes crowded with decaying petals.</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>Size: 15–25cm. Typical bedding-Viola height; three separate plants are recorded in this pot.
 Position: Sun to partial shade. Keep the low flowers open to light beneath the two Skimmias.
@@ -13851,56 +13704,56 @@
 Care priority: Check all three low crowns. Keep the three Rocky Purple Picotee plants clear of fallen Skimmia leaves and inspect each small root plug.</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>The supplied September update and photographs record this plant's identity and position.</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/education-learning/children-young-people/family-activities/grow-it/pansy</t>
         </is>
       </c>
-      <c r="L181" s="2" t="inlineStr">
+      <c r="L179" s="2" t="inlineStr">
         <is>
           <t>lobeliapot-viola-rocky-purple-picotee</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Bed 2/3 Wall Pot</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Viburnum ‘Lisarose’ — label confirmed</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus ‘Lisarose’</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sun to shade. Shelter from cold drying winds</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Check the pot all year. Evergreen Viburnum still loses moisture in winter; water only when the root ball needs it and is unfrozen.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Prune after the winter flowers: Shorten only outgrowing branches after the spring display. Viburnum tinus develops the next flowers on its existing framework. Heavy late-summer or autumn trimming sacrifices buds; removing spent heads also reduces subsequent berries.
 Allow for a shrub-sized root system: Top-dress in spring and repot when roots fill the container. Use a stable, drained loam-based container mix. Check leaf undersides and new shoots for Viburnum beetle damage rather than assuming every hole is drought stress.
 Allow Lisarose room above the Vinca: For this Oak Lodge specimen Keep the wall pot's ivy-like trailer off the Viburnum base and plan greater root room as the shrub grows.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>Spring: Let flowering finish before any shaping, top-dress lightly and inspect for viburnum beetle damage.
 Summer: Water the shared pot deeply during drought and take semi-ripe cuttings only if propagation is wanted.
@@ -13908,12 +13761,12 @@
 Winter: Enjoy the flower clusters and protect the container from prolonged freezing while keeping drainage open.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>‘Lisarose’ is the upright evergreen centre of the new pot between Beds 2 and 3. Deep brick-red buds intensify as temperatures fall, then open to pink-and-white flower clusters from midwinter into spring, followed by dark blue ornamental berries. Its eventual shrub size means the current shared pot is an establishment home rather than unlimited permanent root space.</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>Size: Potentially 2.5–4m. Large dense shrub if planted in open ground
 Position: Sun to shade. Shelter from cold drying winds
@@ -13925,56 +13778,56 @@
 Care priority: Allow Lisarose room above the Vinca. Keep the wall pot's ivy-like trailer off the Viburnum base and plan greater root room as the shrub grows.</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>The photographed label explicitly reads Viburnum Lisarose. This supersedes the earlier unresolved garden record.</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/302763/viburnum-tinus-lisarose-pbr-laurustinus-lisarose/details</t>
         </is>
       </c>
-      <c r="L182" s="2" t="inlineStr">
+      <c r="L180" s="2" t="inlineStr">
         <is>
           <t>bed23wallpot-viburnum-lisarose</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Bed 2/3 Wall Pot</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Vinca minor ‘Illumination’ — label confirmed</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>Vinca minor ‘Illumination’</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sun to shade. Bright shade retains colour without scorching</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Moderate; avoid prolonged drying. Vinca tolerates some dry shade once established, but trailing plants in pots still depend on the container's moisture.</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Keep Vinca runners within bounds: Shorten trails that root into neighbouring planting. Remove unwanted rooted pieces completely. Trim after the main spring flowers, retaining leafy growth for the next display.
 Remove green reversions: Cut all-green shoots back to their point of origin. Variegated forms can be overtaken by vigorous green growth. Give enough light for leaf colour without letting the shallow roots bake.
 Keep the additional Vinca on the wall: For this Oak Lodge specimen Trim rooted runners before this second Illumination leaves its shared wall pot or smothers Lisarose.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>Spring: Trim winter damage, guide fresh runners and enjoy the violet flowers.
 Summer: Shorten stems that reach unwanted soil and keep them clear of the Viburnum crown.
@@ -13982,12 +13835,12 @@
 Winter: Keep drainage holes open and water only when the compost is genuinely dry.</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>This is a second, additional Vinca minor ‘Illumination’, planted to trail over the Bed 2/3 dividing wall while the original remains in the Bed 5 big pot. Broad gold leaf centres edged narrowly in green provide year-round colour, with violet-blue flowers from spring into autumn. Rooting runners make it effective but require deliberate containment.</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Size: 10–15cm high. Trailing stems can extend 60–90cm
 Position: Sun to shade. Bright shade retains colour without scorching
@@ -13999,56 +13852,56 @@
 Care priority: Keep the additional Vinca on the wall. Trim rooted runners before this second Illumination leaves its shared wall pot or smothers Lisarose.</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>The retained name and distinctive gold-centred foliage confirm this additional ‘Illumination’ specimen. This supersedes the earlier unresolved garden record.</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/161486/vinca-minor-illumination-v/details</t>
         </is>
       </c>
-      <c r="L183" s="2" t="inlineStr">
+      <c r="L181" s="2" t="inlineStr">
         <is>
           <t>bed23wallpot-vinca-minor-illumination</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit — label confirmed</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus ‘Anvi’ (Spirit)</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade. Shelter from cold drying winds</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Check the pot all year. Evergreen Viburnum still loses moisture in winter; water only when the root ball needs it and is unfrozen.</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Prune after the winter flowers: Shorten only outgrowing branches after the spring display. Viburnum tinus develops the next flowers on its existing framework. Heavy late-summer or autumn trimming sacrifices buds; removing spent heads also reduces subsequent berries.
 Allow for a shrub-sized root system: Top-dress in spring and repot when roots fill the container. Use a stable, drained loam-based container mix. Check leaf undersides and new shoots for Viburnum beetle damage rather than assuming every hole is drought stress.
 Inspect the separate Spirit pot: For this Oak Lodge specimen Check drainage and root crowding in Spirit's own glazed pot rather than assuming it matches the shared Lisarose container.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Spring: Let flowering finish, then prune only if needed and refresh the top layer of compost.
 Summer: Water deeply through drought, feed lightly and inspect for viburnum beetle or whitefly.
@@ -14056,12 +13909,12 @@
 Winter: Keep the pot drained, protect it from prolonged hard freezes and enjoy the developing flower clusters.</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit (‘Anvi’) fills the new glazed pot at the foot of the steps with glossy evergreen foliage and a long winter display. Pink buds open to lightly fragrant creamy-white clusters from late winter into spring, followed by blue-black ornamental berries. The shrub can reach about two metres, so root room, feeding and winter protection around the pot matter as it matures.</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Size: Up to about 2m. Compact rounded shrub with a similar spread
 Position: Sun or partial shade. Shelter from cold drying winds
@@ -14073,56 +13926,56 @@
 Care priority: Inspect the separate Spirit pot. Check drainage and root crowding in Spirit's own glazed pot rather than assuming it matches the shared Lisarose container.</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>The photographed nursery label reads Viburnum tinus Spirit; ‘Anvi’ is its accepted cultivar epithet. This supersedes the earlier unresolved garden record.</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/196958/viburnum-tinus-spirit-%28anvipbr%29/details</t>
         </is>
       </c>
-      <c r="L184" s="2" t="inlineStr">
+      <c r="L182" s="2" t="inlineStr">
         <is>
           <t>viburnumpot-viburnum-tinus-spirit</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>House · Sitting Room · Rhipsalis (species to confirm)</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Rhipsalis (species to confirm)</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>Rhipsalis sp.</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Bright indirect. Protect the trails from harsh window sun.</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Surface drying. Drain after watering; avoid sustained dryness.</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Check the hanging pot: Feel the compost before watering. Soak when its surface dries, then drain away from furniture.
 Protect its long trails: Keep stems clear of the stairs. The purple star records the hanging point; check that walking past does not snag growth.
 Give filtered light: Avoid harsh direct sunshine. Observe pale or puckered stems and adjust light or moisture after checking the roots.</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Spring: Watch for fresh branching and increase checks as growth resumes.
 Summer: Check the exposed hanging root ball during warm spells.
@@ -14130,12 +13983,12 @@
 Winter: Keep the hanging cactus warm and water less often.</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>The new Rhipsalis hangs beside the sitting-room stair opening, its slender green stems falling in a long curtain. Brad supplied the genus name; species remains unresolved. Care follows mistletoe-cactus guidance provisionally, with observation of this specimen taking priority.</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Habit: Trailing stems. The October photograph shows a hanging specimen.
 Light: Bright indirect. Protect the trails from harsh window sun.
@@ -14145,57 +13998,57 @@
 Care priority: Keep the hanging root ball accessible. Check moisture in the hanging pot itself and keep the long trails clear of the split-level stair opening.</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>Genus supplied by Brad; no species or cultivar claimed from the photograph.</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr">
         <is>
           <t>https://plants.ces.ncsu.edu/plants/rhipsalis-baccifera/
 https://www.rhs.org.uk/plants/14483/rhipsalis-baccifera/details</t>
         </is>
       </c>
-      <c r="L185" s="2" t="inlineStr">
+      <c r="L183" s="2" t="inlineStr">
         <is>
           <t>house-sitting-rhipsalis</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>House · Sitting Room / stair opening · Dracaena Bicolour Touffe</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Dracaena Bicolour Touffe</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>Dracaena marginata Bicolor type — assumed</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Indirect light. Shelter at the stair opening.</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Upper compost drying. Avoid stagnant runoff.</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Water the inner pot: Allow the upper compost to dry. Drain thoroughly and use rainwater where possible.
 Keep leaves out of traffic: Check the green-star stair position. Rotate only enough to maintain balanced growth without obstructing the passage.
 Clean and inspect the tufts: Wipe dust from strap-shaped leaves. Inspect for pests; avoid repeatedly wetting an already damp root ball.</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Spring: Watch the two crowns for new leaves and restart modest feeding.
 Summer: Protect narrow leaves from strong glass-filtered sun and draughts.
@@ -14203,12 +14056,12 @@
 Winter: Keep the stair-side plant warm and reduce watering further.</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Brad’s “Dracena Bicolour Touffe” is recorded as Dracaena Bicolour Touffe. The two narrow-leaved tufts beside the split-level stairs fit a marginata-type dragon tree. The formal Bicolor cultivar relationship remains assumed without a retained passport.</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Habit: Upright leafy tufts. Two crowns are visible in the small pot.
 Light: Indirect light. Shelter at the stair opening.
@@ -14218,57 +14071,57 @@
 Care priority: Protect the two stair-side tufts. Keep leaves clear of passing feet; verify natural light and drain the small inner pot after watering.</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Name supplied by Brad; Dracaena marginata Bicolor type is a qualified photo fit.</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/dracaena/how-to-grow-dracaena
 https://www.rhs.org.uk/plants/dracaena</t>
         </is>
       </c>
-      <c r="L186" s="2" t="inlineStr">
+      <c r="L184" s="2" t="inlineStr">
         <is>
           <t>house-sitting-dracaena-bicolour</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>House · Bedroom-wing landing · Crassula 'Hottentot'</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Crassula 'Hottentot'</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>Crassula rupestris subsp. marnieriana type</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Very bright. The lamp is part of the display; assess actual daylight.</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Dry between drinks. Use the inner-pot weight and compost together.</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Empty the decorative pot: Water only after drying. Soak the inner pot separately and let runoff finish before replacing it.
 Assess daylight at the shelf: Give the succulent strong natural light. Introduce direct sun gradually; watch stretching at the orange-star position.
 Keep the leaf strings sound: Handle trailing growth gently. Remove only damaged portions and inspect tightly stacked leaves for mealybugs.</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>Spring: Resume moderate watering once the leaf strings extend.
 Summer: Maintain bright light and allow drying between soakings.
@@ -14276,12 +14129,12 @@
 Winter: Water the landing succulent sparingly and keep it warm.</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Crassula ‘Hottentot’ spills over the landing shelf in dense bead-like strings of fleshy paired leaves. The supplied commercial name is retained, while its botanical placement follows the marnieriana worm-plant type provisionally. The orange star marks the shelf beside the lamp.</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>Habit: Pendant leafy strings. Long trails spill from the decorative pot.
 Light: Very bright. The lamp is part of the display; assess actual daylight.
@@ -14291,57 +14144,57 @@
 Care priority: Check natural light on the landing shelf. The table lamp does not establish adequate daylight; monitor stretching and let the succulent compost dry between drinks.</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Commercial name supplied by Brad; marnieriana botanical fit remains provisional.</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/4749/crassula-rupestris-subsp-marnieriana/details
 https://powo.science.kew.org/taxon/urn%3Alsid%3Aipni.org%3Anames%3A878790-1</t>
         </is>
       </c>
-      <c r="L187" s="2" t="inlineStr">
+      <c r="L185" s="2" t="inlineStr">
         <is>
           <t>house-landing-crassula-hottentot</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>House · Kitchen / Dining · Philodendron (species to confirm)</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Philodendron (species to confirm)</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Philodendron sp.</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Bright indirect. Protect leaves at the kitchen window.</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Upper compost drying. Use airy compost and free drainage.</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Check the kitchen root ball: Water after surface drying. Drain the orange pot fully before returning it to the window.
 Leave space for new leaves: Protect tender foliage from sun scorch. Observe growth before deciding whether this particular plant needs a climbing support.
 Handle with care: Keep it out of reach. Wear gloves when cutting and clean tools after contact with sap.</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Spring: Record the next leaves to help resolve identity and habit.
 Summer: Check the small kitchen pot more often during warm weather.
@@ -14349,12 +14202,12 @@
 Winter: Keep the Philodendron away from cold window glass.</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>The birthday photograph records a small Philodendron in an orange pot. Brad’s red star places it at the kitchen / dining window. Species, cultivar and eventual climbing or upright habit remain unresolved, so this portrait uses genus guidance and keeps those questions visible.</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Light: Bright indirect. Protect leaves at the kitchen window.
 Water: Upper compost drying. Use airy compost and free drainage.
@@ -14364,56 +14217,56 @@
 Care priority: Record the next kitchen-window leaves. Retain species uncertainty, inspect new growth before choosing a support and keep the orange pot fully drained.</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Philodendron genus supplied by Brad; species and cultivar unresolved.</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/philodendron/growing-guide</t>
         </is>
       </c>
-      <c r="L188" s="2" t="inlineStr">
+      <c r="L186" s="2" t="inlineStr">
         <is>
           <t>house-kitchen-philodendron</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>House · Bedroom-wing landing · Zamioculcas</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Zamioculcas</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>Zamioculcas zamiifolia — assumed</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Indirect; shade tolerated. Lower light lengthens drying time.</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Root ball drying. Check deeply before the next drink.</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Let the root ball dry: Check below the surface. Water thoroughly only after drying and let all runoff escape.
 Protect the landing leaves: Keep upright stalks away from traffic. The blue star sits beside the stair opening; avoid scraping leaflets when passing.
 Inspect glossy leaflets: Wipe dust gently. Look for scale on stalks and leaf undersides; feed sparingly during active growth.</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>Spring: Watch for new upright shoots and check whether the pot is congested.
 Summer: Allow full drying even while the landing is warm.
@@ -14421,12 +14274,12 @@
 Winter: Keep the rhizomes dry between occasional winter drinks.</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Zamioculcas stands beside the console on the bedroom-wing landing, with glossy leaflets on upright fleshy stalks. Its photograph strongly supports Zamioculcas zamiifolia, retained as assumed without a label. The blue star records the position beside Bedroom 3.</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>Habit: Upright glossy leaves. Fleshy stalks rise from underground rhizomes.
 Light: Indirect; shade tolerated. Lower light lengthens drying time.
@@ -14436,24 +14289,24 @@
 Care priority: Let the fleshy rhizomes dry between drinks. Check deep compost at the blue-star landing position before watering; avoid trapping runoff beneath the nursery pot.</t>
         </is>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Supplied genus and glossy pinnate leaves strongly support Z. zamiifolia; retained as assumed.</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr">
         <is>
           <t>https://plants.ces.ncsu.edu/plants/zamioculcas-zamiifolia/</t>
         </is>
       </c>
-      <c r="L189" s="2" t="inlineStr">
+      <c r="L187" s="2" t="inlineStr">
         <is>
           <t>house-landing-zamioculcas</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L189"/>
+  <autoFilter ref="A1:L187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -1485,69 +1485,68 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia (cultivar to confirm)</t>
+          <t>Pernettya Pink (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia hybrid</t>
+          <t>Gaultheria mucronata — pink-fruited form</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sheltered partial shade. Back Bed 1 beneath the Japanese Maple</t>
+          <t>Sun to partial shade. Monitor shade beneath the Maple; record whether this pocket gets sufficient light.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Moist during active Bed 1 growth. The former basket root ball needs establishment water, but the sheltered crown must not sit in cold wet soil.</t>
+          <t>Even moisture at roots. Check this new planting separately from its established neighbours.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Wait for spring buds before pruning: Cut winter-damaged stems back only after living growth is visible. The cultivar and hardiness are unresolved. Preserve useful low buds and pinch young shoots only if a bushier border framework is needed.
-Support the arching flowers: Keep Fuchsia stems clear of the fern and Skimmia crowns. Deadhead during the mild season, feed lightly only while growing and photograph open flowers from the side and front for later identification.
-Support the moved Bed 1 stems: For this Oak Lodge specimen Arrange the arching Fuchsia clear of the fern and Skimmia crowns while its new root system establishes.</t>
+          <t>Check the acidic pocket: Test soil pH if it is unknown. Use an acidic root environment for Pernettya; if this bed is unsuitable, an ericaceous container is a practical alternative.
+Keep berry-bearing growth: Avoid a hard autumn trim. Remove damaged shoots and control unwanted suckers. Keep the small plant clear of expanding Hosta leaves.
+Check future pollination: Existing berries do not guarantee next year’s crop. Female Gaultheria mucronata normally needs a compatible male nearby; confirm the selection before buying a partner.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Spring: Wait for live buds before cutting winter-damaged stems, then pinch young shoots only if a bushier Bed 1 framework is needed.
-Summer: Water the new root area during dry spells, feed lightly while flowering and support arching stems away from the fern crown.
-Autumn: Stop feeding, record a fully open flower for identification and mulch lightly without covering the stem base.
-Winter: Protect the newly planted crown until its hardiness is known and wait for spring buds before declaring bare upper stems dead.</t>
+          <t>Spring: Check new shoots and remove unwanted suckers without disturbing the Pernettya root ball.
+Summer: Watch the little bell flowers and check moisture beneath the Maple as its canopy fills.
+Autumn: Enjoy the photographed pink fruit and keep bark away from the Pernettya stem base.
+Winter: Check that the evergreen Pernettya root ball drains freely and does not dry during prolonged dry weather.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>The former Hanging Basket 3 Fuchsia now grows beneath the Japanese Maple in Back Bed 1, where its arching stems carry pendant bicolour flowers among the newly moved fern and Skimmia. The trailing habit is secure, but colour and cultivar are not recorded, so final size and winter hardiness remain deliberately unresolved.</t>
+          <t>Pernettya Pink brings pale pink and stronger pink berries to the cleared pocket beside the Buddha beneath the Japanese Maple. Brad supplied the name; the photograph fits a pink-fruited Gaultheria mucronata, but does not establish a named cultivar such as Pink Pearl. It replaces part of the space left by the discarded September Fuchsia and fern.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Size: 20–60cm high. Arching stems may spread beyond the former basket scale
-Position: Sheltered partial shade. Back Bed 1 beneath the Japanese Maple
-Soil: Moist and well-drained. Humus-rich bed soil with reliable drainage
-Hardiness: To confirm. The cultivar is unresolved; protect the crown during its first winter in the bed
-Main feature: Pendant bicolour flowers. Arching flowers among the shaded Bed 1 planting
-Identity: Fuchsia cultivar. Cultivar and exact flower colours are not recorded
-Water: Moist during active Bed 1 growth. The former basket root ball needs establishment water, but the sheltered crown must not sit in cold wet soil.
-Care priority: Support the moved Bed 1 stems. Arrange the arching Fuchsia clear of the fern and Skimmia crowns while its new root system establishes.</t>
+          <t>Identity: Pink-fruited Gaultheria. Pernettya is an older name; Pink does not identify a particular cultivar.
+Size: About 0.5–1m. Cultivar size remains unresolved; record this specimen’s spread.
+Position: Sun to partial shade. Monitor shade beneath the Maple; record whether this pocket gets sufficient light.
+Soil: Acidic, moist and drained. Check pH before relying on the bed for long-term ericaceous growth.
+Hardiness: Hardy species. Pink-form cultivar rating not confirmed.
+Flower: White bells · late spring / early summer. The pink display is fruit, not flowers.
+Water: Even moisture at roots. Check this new planting separately from its established neighbours.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia identity and its move from Hanging Basket 3 to Back Bed 1 are secure from the garden record; cultivar is unresolved.</t>
+          <t>Name supplied by Brad, October 2026. Photos support the plant group and berry colour; cultivar confirmation remains pending.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/84426/fuchsia-mrs-popple/details</t>
+          <t>https://www.rhs.org.uk/plants/67076/gaultheria-mucronata-pink-pearl-f/details</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>baskets-trailing-fuchsia</t>
+          <t>bed1-pernettya-pink</t>
         </is>
       </c>
     </row>
@@ -1559,69 +1558,69 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fern (cultivar to confirm)</t>
+          <t>Solanum 'Jupiter' (name supplied)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fern — cultivar to confirm</t>
+          <t>Solanum pseudocapsicum 'Jupiter' — supplied trade name</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sheltered shade to partial shade. Filtered light protects soft fronds while its exact shade preference remains unresolved.</t>
+          <t>Sunny, sheltered position. Monitor shade beneath the Maple; record whether this pocket gets sufficient light.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Even moisture in sheltered soil. The moved fern needs a cool root area beneath the Maple but its crown must not remain saturated.</t>
+          <t>Even moisture at roots. Check this new planting separately from its established neighbours.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Protect the moved frond crown: Remove only dead fronds at their base and clear fallen Maple leaves. Do not shear the plant or feed it for flowers. Brown spore patches can be normal; keep the crown exposed to air as it establishes in Bed 1.
-Use new growth for identification: Photograph croziers, scales and mature frond undersides. Until the species is resolved, protect the new planting during hard frost rather than assuming the hardiness of a known garden fern.
-Keep a frond for identification: For this Oak Lodge specimen Photograph the moved Bed 1 fern's underside before removing old fronds; its winter requirements are still unresolved.</t>
+          <t>Plan for frost: Arrange frost-free accommodation if keeping Jupiter. It is recorded as planted in Bed 1, but is a seasonal outdoor display unless suitable frost-free accommodation becomes available.
+Water its own root ball: Feel the soil before adding water. The nursery root ball can dry while surrounding bark and soil look damp. Keep drainage open and reduce watering in cool conditions.
+Handle fruit safely: Keep children and pets away from the berries. All parts are poisonous. Wear gloves, collect fallen berries and never treat the fruit as food.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Spring: Remove only brown fronds at their base and photograph new croziers, scales and mature frond undersides to narrow the identification.
-Summer: Use the Maple canopy as shelter from hot midday sun, maintaining even moisture while keeping the crown open to air.
-Autumn: Clear fallen leaves before they smother the crown and record whether the fronds remain evergreen as temperatures fall.
-Winter: Because the species is unconfirmed, add light protection during hard frost and keep the sheltered crown just moist rather than saturated.</t>
+          <t>Spring: If Jupiter has survived frost-free, inspect living growth before any light shaping.
+Summer: Give Jupiter good light during flowering; inspect leaves for aphids and mites.
+Autumn: Enjoy Jupiter’s orange and red fruit; arrange frost-free conditions before damaging cold.
+Winter: If retained frost-free, give Jupiter bright light and reduced watering; assess outdoor frost damage before deciding its future.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>The unidentified fern moved from Hanging Basket 3 into the sheltered soil beneath the Japanese Maple in Back Bed 1. Its divided green fronds now form a low foliage layer beside the moved Fuchsia and Skimmia. Brown spore patches can be normal, but species and hardiness remain unresolved, so preserve diagnostic photographs and use cautious first-winter protection.</t>
+          <t>Solanum Jupiter adds bright green, yellow, orange and red fruit in front of the Hosta in the cleared Bed 1 pocket. The supplied name and photograph fit the ornamental winter-cherry group, Solanum pseudocapsicum. Jupiter is recorded as Brad’s supplied trade name, with a label still needed for confirmation. This is a tender seasonal planting.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Size: Species not yet identified. Measure the fronds and record their form; basket size is not a mature plant dimension.
-Position: Sheltered shade to partial shade. Filtered light protects soft fronds while its exact shade preference remains unresolved.
-Soil: Humus-rich, moist and free-draining soil. Keep the frond-producing crown above the compost and prevent the small root plug drying hard.
-Hardiness: Unresolved; protect from frost. An unidentified fern must not inherit the hardy Dryopteris rating.
-Main feature: Divided green fronds. Fronds are the display: this fern produces spores, not flowers.
-Identity: Fern (cultivar to confirm). Name retained from the supplied garden record
-Water: Even moisture in sheltered soil. The moved fern needs a cool root area beneath the Maple but its crown must not remain saturated.
-Care priority: Keep a frond for identification. Photograph the moved Bed 1 fern's underside before removing old fronds; its winter requirements are still unresolved.</t>
+          <t>Identity: Jupiter · name supplied. Brad supplied Jupiter; no label photograph confirms the name.
+Size: Species can reach about 0.9m. Nursery selections may stay smaller; record the height of this plant.
+Position: Sunny, sheltered position. Monitor shade beneath the Maple; record whether this pocket gets sufficient light.
+Soil: Moist, well-drained loam. Water the small root ball without keeping the planting hole saturated.
+Hardiness: Tender; frost-free winter. An outdoor wall or fleece cannot guarantee frost-free conditions.
+Flower: White stars · summer. The coloured balls are ornamental fruit, not edible tomatoes.
+Water: Even moisture at roots. Check this new planting separately from its established neighbours.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>The supplied September update and photographs record this plant's identity and position.</t>
+          <t>Name supplied by Brad, October 2026. Photos support the plant group and berry colour; cultivar confirmation remains pending.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/types/ferns/growing-guide</t>
+          <t>https://plants.ces.ncsu.edu/plants/solanum-pseudocapsicum/
+https://pages.nxtbook.com/syngenta/FloriProServices/Pot_Plants_2016_EX/offline/FloriProServices_Pot_Plants_2016_EX.pdf</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>baskets-fern-unidentified</t>
+          <t>bed1-solanum-jupiter</t>
         </is>
       </c>
     </row>
